--- a/src/0622/master.xlsx
+++ b/src/0622/master.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38309458-5500-430B-9E46-5C92E42514C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{4EE9A253-AC4A-4A8E-ACFC-E21FBE1DE8E4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{4EE9A253-AC4A-4A8E-ACFC-E21FBE1DE8E4}"/>
   </bookViews>
   <sheets>
     <sheet name="T_常設機器一覧" sheetId="1" r:id="rId1"/>
@@ -9204,24 +9204,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -9243,47 +9225,30 @@
     <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{391A8BC1-E331-454A-9C8C-AD9956E4B3A9}"/>
   </cellStyles>
   <dxfs count="49">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -9509,6 +9474,41 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -10695,14 +10695,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{54C859F2-11DE-4036-9750-40E8E17D8E8F}" name="T_通信機器等" displayName="T_通信機器等" ref="A1:H74" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:H74" xr:uid="{54C859F2-11DE-4036-9750-40E8E17D8E8F}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D2F12FEA-7261-4628-B244-6EA0866ED211}" name="部屋名" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{191441F3-009F-49FD-85C6-83C9ED7F7EED}" name="名称" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{9CA2830B-04C7-42B8-B8AF-C39178E099FB}" name="メーカ" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{714A81CD-5E52-4294-A02F-CA4EBC21933C}" name="型式" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{387E76C3-2194-4955-9B4D-0C42D5F70A05}" name="全社連番" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{046BEBB1-94E0-45E5-BE2C-BB0D0022711B}" name="管理No." dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{07108A07-816C-4EDB-882E-278A1C06FAC2}" name="管理部署" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{2DF3BCF5-8397-47F6-AF98-A961D2293397}" name="有効期限" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D2F12FEA-7261-4628-B244-6EA0866ED211}" name="部屋名" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{191441F3-009F-49FD-85C6-83C9ED7F7EED}" name="名称" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{9CA2830B-04C7-42B8-B8AF-C39178E099FB}" name="メーカ" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{714A81CD-5E52-4294-A02F-CA4EBC21933C}" name="型式" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{387E76C3-2194-4955-9B4D-0C42D5F70A05}" name="全社連番" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{046BEBB1-94E0-45E5-BE2C-BB0D0022711B}" name="管理No." dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{07108A07-816C-4EDB-882E-278A1C06FAC2}" name="管理部署" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{2DF3BCF5-8397-47F6-AF98-A961D2293397}" name="有効期限" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17249,7 +17249,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="18" customHeight="1">
-      <c r="A89" s="44" t="s">
+      <c r="A89" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -17275,7 +17275,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="18" customHeight="1">
-      <c r="A90" s="44" t="s">
+      <c r="A90" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -17301,7 +17301,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="18" customHeight="1">
-      <c r="A91" s="44" t="s">
+      <c r="A91" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B91" s="2" t="s">
@@ -17327,7 +17327,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="18" customHeight="1">
-      <c r="A92" s="44" t="s">
+      <c r="A92" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B92" s="2" t="s">
@@ -17353,7 +17353,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="18" customHeight="1">
-      <c r="A93" s="44" t="s">
+      <c r="A93" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -17379,7 +17379,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="18" customHeight="1">
-      <c r="A94" s="44" t="s">
+      <c r="A94" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -17405,7 +17405,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="18" customHeight="1">
-      <c r="A95" s="44" t="s">
+      <c r="A95" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B95" s="2" t="s">
@@ -17431,7 +17431,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="18" customHeight="1">
-      <c r="A96" s="44" t="s">
+      <c r="A96" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B96" s="2" t="s">
@@ -17457,7 +17457,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="18" customHeight="1">
-      <c r="A97" s="44" t="s">
+      <c r="A97" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -17483,7 +17483,7 @@
       </c>
     </row>
     <row r="98" spans="1:8" ht="18" customHeight="1">
-      <c r="A98" s="44" t="s">
+      <c r="A98" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B98" s="2" t="s">
@@ -17509,7 +17509,7 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="18" customHeight="1">
-      <c r="A99" s="44" t="s">
+      <c r="A99" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B99" s="20" t="s">
@@ -17535,7 +17535,7 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="18" customHeight="1">
-      <c r="A100" s="44" t="s">
+      <c r="A100" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -17561,7 +17561,7 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="18" customHeight="1">
-      <c r="A101" s="44" t="s">
+      <c r="A101" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -17587,7 +17587,7 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="18" customHeight="1">
-      <c r="A102" s="44" t="s">
+      <c r="A102" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -17613,7 +17613,7 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="18" customHeight="1">
-      <c r="A103" s="44" t="s">
+      <c r="A103" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -17639,7 +17639,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="18" customHeight="1">
-      <c r="A104" s="44" t="s">
+      <c r="A104" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -17665,7 +17665,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="18" customHeight="1">
-      <c r="A105" s="44" t="s">
+      <c r="A105" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -17691,7 +17691,7 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="18" customHeight="1">
-      <c r="A106" s="44" t="s">
+      <c r="A106" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -17717,7 +17717,7 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1">
-      <c r="A107" s="44" t="s">
+      <c r="A107" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -17743,7 +17743,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="18" customHeight="1">
-      <c r="A108" s="44" t="s">
+      <c r="A108" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -17769,7 +17769,7 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="18" customHeight="1">
-      <c r="A109" s="44" t="s">
+      <c r="A109" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -17795,7 +17795,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="18" customHeight="1">
-      <c r="A110" s="44" t="s">
+      <c r="A110" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -17821,7 +17821,7 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="18" customHeight="1">
-      <c r="A111" s="44" t="s">
+      <c r="A111" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -17847,7 +17847,7 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="18" customHeight="1">
-      <c r="A112" s="44" t="s">
+      <c r="A112" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -17873,7 +17873,7 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="18" customHeight="1">
-      <c r="A113" s="44" t="s">
+      <c r="A113" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -17899,7 +17899,7 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="18" customHeight="1">
-      <c r="A114" s="44" t="s">
+      <c r="A114" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -17925,7 +17925,7 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="18" customHeight="1">
-      <c r="A115" s="44" t="s">
+      <c r="A115" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B115" s="12" t="s">
@@ -17951,7 +17951,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="18" customHeight="1">
-      <c r="A116" s="44" t="s">
+      <c r="A116" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B116" s="30" t="s">
@@ -17977,7 +17977,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="18" customHeight="1">
-      <c r="A117" s="44" t="s">
+      <c r="A117" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B117" s="12" t="s">
@@ -18003,7 +18003,7 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="18" customHeight="1">
-      <c r="A118" s="44" t="s">
+      <c r="A118" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B118" s="30" t="s">
@@ -18029,7 +18029,7 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="18" customHeight="1">
-      <c r="A119" s="44" t="s">
+      <c r="A119" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B119" s="2" t="s">
@@ -18055,7 +18055,7 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="18" customHeight="1">
-      <c r="A120" s="44" t="s">
+      <c r="A120" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B120" s="2" t="s">
@@ -18081,7 +18081,7 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="18" customHeight="1">
-      <c r="A121" s="44" t="s">
+      <c r="A121" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -18107,7 +18107,7 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="18" customHeight="1">
-      <c r="A122" s="44" t="s">
+      <c r="A122" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -18133,7 +18133,7 @@
       </c>
     </row>
     <row r="123" spans="1:8" ht="18" customHeight="1">
-      <c r="A123" s="44" t="s">
+      <c r="A123" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -18159,7 +18159,7 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="18" customHeight="1">
-      <c r="A124" s="44" t="s">
+      <c r="A124" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -18185,7 +18185,7 @@
       </c>
     </row>
     <row r="125" spans="1:8" ht="18" customHeight="1">
-      <c r="A125" s="44" t="s">
+      <c r="A125" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -18211,7 +18211,7 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="18" customHeight="1">
-      <c r="A126" s="44" t="s">
+      <c r="A126" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -18237,7 +18237,7 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="18" customHeight="1">
-      <c r="A127" s="44" t="s">
+      <c r="A127" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -18263,7 +18263,7 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="18" customHeight="1">
-      <c r="A128" s="44" t="s">
+      <c r="A128" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B128" s="2" t="s">
@@ -18289,7 +18289,7 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="18" customHeight="1">
-      <c r="A129" s="44" t="s">
+      <c r="A129" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B129" s="2" t="s">
@@ -18315,7 +18315,7 @@
       </c>
     </row>
     <row r="130" spans="1:8" ht="18" customHeight="1">
-      <c r="A130" s="44" t="s">
+      <c r="A130" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B130" s="2" t="s">
@@ -18341,7 +18341,7 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="18" customHeight="1">
-      <c r="A131" s="44" t="s">
+      <c r="A131" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B131" s="2" t="s">
@@ -18367,7 +18367,7 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="18" customHeight="1">
-      <c r="A132" s="44" t="s">
+      <c r="A132" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B132" s="2" t="s">
@@ -18393,7 +18393,7 @@
       </c>
     </row>
     <row r="133" spans="1:8" ht="18" customHeight="1">
-      <c r="A133" s="44" t="s">
+      <c r="A133" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B133" s="2" t="s">
@@ -18419,7 +18419,7 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="18" customHeight="1">
-      <c r="A134" s="44" t="s">
+      <c r="A134" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B134" s="2" t="s">
@@ -18445,7 +18445,7 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="18" customHeight="1">
-      <c r="A135" s="44" t="s">
+      <c r="A135" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B135" s="2" t="s">
@@ -18471,7 +18471,7 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="18" customHeight="1">
-      <c r="A136" s="44" t="s">
+      <c r="A136" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B136" s="2" t="s">
@@ -18497,7 +18497,7 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="18" customHeight="1">
-      <c r="A137" s="44" t="s">
+      <c r="A137" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B137" s="2" t="s">
@@ -18523,7 +18523,7 @@
       </c>
     </row>
     <row r="138" spans="1:8" ht="18" customHeight="1">
-      <c r="A138" s="44" t="s">
+      <c r="A138" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B138" s="2" t="s">
@@ -18549,7 +18549,7 @@
       </c>
     </row>
     <row r="139" spans="1:8" ht="18" customHeight="1">
-      <c r="A139" s="44" t="s">
+      <c r="A139" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B139" s="2" t="s">
@@ -18575,7 +18575,7 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="18" customHeight="1">
-      <c r="A140" s="44" t="s">
+      <c r="A140" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B140" s="2" t="s">
@@ -18601,7 +18601,7 @@
       </c>
     </row>
     <row r="141" spans="1:8" ht="18" customHeight="1">
-      <c r="A141" s="44" t="s">
+      <c r="A141" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B141" s="2" t="s">
@@ -18627,7 +18627,7 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="18" customHeight="1">
-      <c r="A142" s="44" t="s">
+      <c r="A142" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B142" s="2" t="s">
@@ -18653,7 +18653,7 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="18" customHeight="1">
-      <c r="A143" s="44" t="s">
+      <c r="A143" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B143" s="20" t="s">
@@ -18679,7 +18679,7 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="18" customHeight="1">
-      <c r="A144" s="44" t="s">
+      <c r="A144" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B144" s="2" t="s">
@@ -18705,7 +18705,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="18" customHeight="1">
-      <c r="A145" s="44" t="s">
+      <c r="A145" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B145" s="2" t="s">
@@ -18731,7 +18731,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="18" customHeight="1">
-      <c r="A146" s="44" t="s">
+      <c r="A146" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B146" s="2" t="s">
@@ -18757,7 +18757,7 @@
       </c>
     </row>
     <row r="147" spans="1:8" ht="18" customHeight="1">
-      <c r="A147" s="44" t="s">
+      <c r="A147" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B147" s="2" t="s">
@@ -18783,7 +18783,7 @@
       </c>
     </row>
     <row r="148" spans="1:8" ht="18" customHeight="1">
-      <c r="A148" s="44" t="s">
+      <c r="A148" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B148" s="2" t="s">
@@ -18809,7 +18809,7 @@
       </c>
     </row>
     <row r="149" spans="1:8" ht="18" customHeight="1">
-      <c r="A149" s="44" t="s">
+      <c r="A149" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B149" s="2" t="s">
@@ -18835,7 +18835,7 @@
       </c>
     </row>
     <row r="150" spans="1:8" ht="18" customHeight="1">
-      <c r="A150" s="44" t="s">
+      <c r="A150" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B150" s="2" t="s">
@@ -18861,7 +18861,7 @@
       </c>
     </row>
     <row r="151" spans="1:8" ht="18" customHeight="1">
-      <c r="A151" s="44" t="s">
+      <c r="A151" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B151" s="2" t="s">
@@ -18887,7 +18887,7 @@
       </c>
     </row>
     <row r="152" spans="1:8" ht="18" customHeight="1">
-      <c r="A152" s="44" t="s">
+      <c r="A152" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -18913,7 +18913,7 @@
       </c>
     </row>
     <row r="153" spans="1:8" ht="18" customHeight="1">
-      <c r="A153" s="44" t="s">
+      <c r="A153" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B153" s="2" t="s">
@@ -18939,7 +18939,7 @@
       </c>
     </row>
     <row r="154" spans="1:8" ht="18" customHeight="1">
-      <c r="A154" s="44" t="s">
+      <c r="A154" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -18965,7 +18965,7 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="18" customHeight="1">
-      <c r="A155" s="44" t="s">
+      <c r="A155" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -18991,7 +18991,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" ht="18" customHeight="1">
-      <c r="A156" s="44" t="s">
+      <c r="A156" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -19017,7 +19017,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" ht="18" customHeight="1">
-      <c r="A157" s="44" t="s">
+      <c r="A157" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B157" s="2" t="s">
@@ -19043,7 +19043,7 @@
       </c>
     </row>
     <row r="158" spans="1:8" ht="18" customHeight="1">
-      <c r="A158" s="44" t="s">
+      <c r="A158" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B158" s="2" t="s">
@@ -19069,7 +19069,7 @@
       </c>
     </row>
     <row r="159" spans="1:8" ht="18" customHeight="1">
-      <c r="A159" s="44" t="s">
+      <c r="A159" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B159" s="2" t="s">
@@ -19095,7 +19095,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="18" customHeight="1">
-      <c r="A160" s="44" t="s">
+      <c r="A160" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B160" s="2" t="s">
@@ -19121,7 +19121,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="18" customHeight="1">
-      <c r="A161" s="44" t="s">
+      <c r="A161" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B161" s="2" t="s">
@@ -19147,7 +19147,7 @@
       </c>
     </row>
     <row r="162" spans="1:8" ht="18" customHeight="1">
-      <c r="A162" s="44" t="s">
+      <c r="A162" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B162" s="2" t="s">
@@ -19173,7 +19173,7 @@
       </c>
     </row>
     <row r="163" spans="1:8" ht="18" customHeight="1">
-      <c r="A163" s="44" t="s">
+      <c r="A163" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B163" s="2" t="s">
@@ -19199,7 +19199,7 @@
       </c>
     </row>
     <row r="164" spans="1:8" ht="18" customHeight="1">
-      <c r="A164" s="44" t="s">
+      <c r="A164" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -19225,7 +19225,7 @@
       </c>
     </row>
     <row r="165" spans="1:8" ht="18" customHeight="1">
-      <c r="A165" s="44" t="s">
+      <c r="A165" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B165" s="2" t="s">
@@ -19251,7 +19251,7 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="18" customHeight="1">
-      <c r="A166" s="44" t="s">
+      <c r="A166" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B166" s="2" t="s">
@@ -19277,7 +19277,7 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="18" customHeight="1">
-      <c r="A167" s="44" t="s">
+      <c r="A167" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B167" s="2" t="s">
@@ -19303,7 +19303,7 @@
       </c>
     </row>
     <row r="168" spans="1:8" ht="18" customHeight="1">
-      <c r="A168" s="44" t="s">
+      <c r="A168" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B168" s="2" t="s">
@@ -19329,7 +19329,7 @@
       </c>
     </row>
     <row r="169" spans="1:8" ht="18" customHeight="1">
-      <c r="A169" s="44" t="s">
+      <c r="A169" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B169" s="2" t="s">
@@ -19355,7 +19355,7 @@
       </c>
     </row>
     <row r="170" spans="1:8" ht="18" customHeight="1">
-      <c r="A170" s="44" t="s">
+      <c r="A170" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B170" s="2" t="s">
@@ -19381,7 +19381,7 @@
       </c>
     </row>
     <row r="171" spans="1:8" ht="18" customHeight="1">
-      <c r="A171" s="44" t="s">
+      <c r="A171" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B171" s="2" t="s">
@@ -19407,7 +19407,7 @@
       </c>
     </row>
     <row r="172" spans="1:8" ht="18" customHeight="1">
-      <c r="A172" s="44" t="s">
+      <c r="A172" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B172" s="2" t="s">
@@ -19433,7 +19433,7 @@
       </c>
     </row>
     <row r="173" spans="1:8" ht="18" customHeight="1">
-      <c r="A173" s="44" t="s">
+      <c r="A173" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B173" s="2" t="s">
@@ -19459,7 +19459,7 @@
       </c>
     </row>
     <row r="174" spans="1:8" ht="18" customHeight="1">
-      <c r="A174" s="44" t="s">
+      <c r="A174" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B174" s="2" t="s">
@@ -19485,7 +19485,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="18" customHeight="1">
-      <c r="A175" s="44" t="s">
+      <c r="A175" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B175" s="2" t="s">
@@ -19511,7 +19511,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="18" customHeight="1">
-      <c r="A176" s="44" t="s">
+      <c r="A176" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B176" s="2" t="s">
@@ -19537,7 +19537,7 @@
       </c>
     </row>
     <row r="177" spans="1:8" ht="18" customHeight="1">
-      <c r="A177" s="44" t="s">
+      <c r="A177" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B177" s="2" t="s">
@@ -19563,7 +19563,7 @@
       </c>
     </row>
     <row r="178" spans="1:8" ht="18" customHeight="1">
-      <c r="A178" s="44" t="s">
+      <c r="A178" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B178" s="2" t="s">
@@ -19589,7 +19589,7 @@
       </c>
     </row>
     <row r="179" spans="1:8" ht="18" customHeight="1">
-      <c r="A179" s="44" t="s">
+      <c r="A179" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B179" s="2" t="s">
@@ -19615,7 +19615,7 @@
       </c>
     </row>
     <row r="180" spans="1:8" ht="18" customHeight="1">
-      <c r="A180" s="44" t="s">
+      <c r="A180" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B180" s="2" t="s">
@@ -19641,7 +19641,7 @@
       </c>
     </row>
     <row r="181" spans="1:8" ht="18" customHeight="1">
-      <c r="A181" s="44" t="s">
+      <c r="A181" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B181" s="2" t="s">
@@ -19667,7 +19667,7 @@
       </c>
     </row>
     <row r="182" spans="1:8" ht="18" customHeight="1">
-      <c r="A182" s="44" t="s">
+      <c r="A182" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B182" s="2" t="s">
@@ -19693,7 +19693,7 @@
       </c>
     </row>
     <row r="183" spans="1:8" ht="18" customHeight="1">
-      <c r="A183" s="44" t="s">
+      <c r="A183" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B183" s="2" t="s">
@@ -19719,7 +19719,7 @@
       </c>
     </row>
     <row r="184" spans="1:8" ht="18" customHeight="1">
-      <c r="A184" s="44" t="s">
+      <c r="A184" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B184" s="2" t="s">
@@ -19745,7 +19745,7 @@
       </c>
     </row>
     <row r="185" spans="1:8" ht="18" customHeight="1">
-      <c r="A185" s="44" t="s">
+      <c r="A185" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B185" s="2" t="s">
@@ -19771,7 +19771,7 @@
       </c>
     </row>
     <row r="186" spans="1:8" ht="18" customHeight="1">
-      <c r="A186" s="44" t="s">
+      <c r="A186" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B186" s="2" t="s">
@@ -19797,7 +19797,7 @@
       </c>
     </row>
     <row r="187" spans="1:8" ht="18" customHeight="1">
-      <c r="A187" s="44" t="s">
+      <c r="A187" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B187" s="2" t="s">
@@ -19823,7 +19823,7 @@
       </c>
     </row>
     <row r="188" spans="1:8" ht="18" customHeight="1">
-      <c r="A188" s="44" t="s">
+      <c r="A188" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B188" s="2" t="s">
@@ -19849,7 +19849,7 @@
       </c>
     </row>
     <row r="189" spans="1:8" ht="18" customHeight="1">
-      <c r="A189" s="44" t="s">
+      <c r="A189" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B189" s="2" t="s">
@@ -19875,7 +19875,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="18" customHeight="1">
-      <c r="A190" s="44" t="s">
+      <c r="A190" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B190" s="2" t="s">
@@ -19901,7 +19901,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="18" customHeight="1">
-      <c r="A191" s="44" t="s">
+      <c r="A191" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B191" s="2" t="s">
@@ -19927,7 +19927,7 @@
       </c>
     </row>
     <row r="192" spans="1:8" ht="18" customHeight="1">
-      <c r="A192" s="44" t="s">
+      <c r="A192" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B192" s="2" t="s">
@@ -19953,7 +19953,7 @@
       </c>
     </row>
     <row r="193" spans="1:8" ht="18" customHeight="1">
-      <c r="A193" s="44" t="s">
+      <c r="A193" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B193" s="2" t="s">
@@ -19979,7 +19979,7 @@
       </c>
     </row>
     <row r="194" spans="1:8" ht="18" customHeight="1">
-      <c r="A194" s="44" t="s">
+      <c r="A194" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B194" s="2" t="s">
@@ -20005,7 +20005,7 @@
       </c>
     </row>
     <row r="195" spans="1:8" ht="18" customHeight="1">
-      <c r="A195" s="44" t="s">
+      <c r="A195" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B195" s="2" t="s">
@@ -20031,7 +20031,7 @@
       </c>
     </row>
     <row r="196" spans="1:8" ht="18" customHeight="1">
-      <c r="A196" s="44" t="s">
+      <c r="A196" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B196" s="2" t="s">
@@ -20057,7 +20057,7 @@
       </c>
     </row>
     <row r="197" spans="1:8" ht="18" customHeight="1">
-      <c r="A197" s="44" t="s">
+      <c r="A197" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B197" s="2" t="s">
@@ -20083,7 +20083,7 @@
       </c>
     </row>
     <row r="198" spans="1:8" ht="18" customHeight="1">
-      <c r="A198" s="44" t="s">
+      <c r="A198" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B198" s="2" t="s">
@@ -20109,7 +20109,7 @@
       </c>
     </row>
     <row r="199" spans="1:8" ht="18" customHeight="1">
-      <c r="A199" s="44" t="s">
+      <c r="A199" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B199" s="2" t="s">
@@ -20135,7 +20135,7 @@
       </c>
     </row>
     <row r="200" spans="1:8" ht="18" customHeight="1">
-      <c r="A200" s="44" t="s">
+      <c r="A200" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B200" s="2" t="s">
@@ -20161,7 +20161,7 @@
       </c>
     </row>
     <row r="201" spans="1:8" ht="18" customHeight="1">
-      <c r="A201" s="44" t="s">
+      <c r="A201" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B201" s="2" t="s">
@@ -20187,7 +20187,7 @@
       </c>
     </row>
     <row r="202" spans="1:8" ht="18" customHeight="1">
-      <c r="A202" s="44" t="s">
+      <c r="A202" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B202" s="2" t="s">
@@ -20213,7 +20213,7 @@
       </c>
     </row>
     <row r="203" spans="1:8" ht="18" customHeight="1">
-      <c r="A203" s="44" t="s">
+      <c r="A203" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B203" s="2" t="s">
@@ -20239,7 +20239,7 @@
       </c>
     </row>
     <row r="204" spans="1:8" ht="18" customHeight="1">
-      <c r="A204" s="44" t="s">
+      <c r="A204" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B204" s="2" t="s">
@@ -20265,7 +20265,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="18" customHeight="1">
-      <c r="A205" s="44" t="s">
+      <c r="A205" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B205" s="2" t="s">
@@ -20291,7 +20291,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="18" customHeight="1">
-      <c r="A206" s="44" t="s">
+      <c r="A206" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B206" s="2" t="s">
@@ -20317,7 +20317,7 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="18" customHeight="1">
-      <c r="A207" s="44" t="s">
+      <c r="A207" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B207" s="2" t="s">
@@ -20343,7 +20343,7 @@
       </c>
     </row>
     <row r="208" spans="1:8" ht="18" customHeight="1">
-      <c r="A208" s="44" t="s">
+      <c r="A208" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B208" s="2" t="s">
@@ -20369,7 +20369,7 @@
       </c>
     </row>
     <row r="209" spans="1:8" ht="18" customHeight="1">
-      <c r="A209" s="44" t="s">
+      <c r="A209" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B209" s="2" t="s">
@@ -20395,7 +20395,7 @@
       </c>
     </row>
     <row r="210" spans="1:8" ht="18" customHeight="1">
-      <c r="A210" s="44" t="s">
+      <c r="A210" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B210" s="2" t="s">
@@ -20421,7 +20421,7 @@
       </c>
     </row>
     <row r="211" spans="1:8" ht="18" customHeight="1">
-      <c r="A211" s="44" t="s">
+      <c r="A211" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B211" s="2" t="s">
@@ -20447,7 +20447,7 @@
       </c>
     </row>
     <row r="212" spans="1:8" ht="18" customHeight="1">
-      <c r="A212" s="44" t="s">
+      <c r="A212" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B212" s="2" t="s">
@@ -20473,7 +20473,7 @@
       </c>
     </row>
     <row r="213" spans="1:8" ht="18" customHeight="1">
-      <c r="A213" s="44" t="s">
+      <c r="A213" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B213" s="2" t="s">
@@ -20499,7 +20499,7 @@
       </c>
     </row>
     <row r="214" spans="1:8" ht="18" customHeight="1">
-      <c r="A214" s="44" t="s">
+      <c r="A214" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B214" s="2" t="s">
@@ -20525,7 +20525,7 @@
       </c>
     </row>
     <row r="215" spans="1:8" ht="18" customHeight="1">
-      <c r="A215" s="44" t="s">
+      <c r="A215" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B215" s="2" t="s">
@@ -20551,7 +20551,7 @@
       </c>
     </row>
     <row r="216" spans="1:8" ht="18" customHeight="1">
-      <c r="A216" s="44" t="s">
+      <c r="A216" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B216" s="2" t="s">
@@ -20577,7 +20577,7 @@
       </c>
     </row>
     <row r="217" spans="1:8" ht="18" customHeight="1">
-      <c r="A217" s="44" t="s">
+      <c r="A217" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B217" s="2" t="s">
@@ -20603,7 +20603,7 @@
       </c>
     </row>
     <row r="218" spans="1:8" ht="18" customHeight="1">
-      <c r="A218" s="44" t="s">
+      <c r="A218" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B218" s="2" t="s">
@@ -20629,7 +20629,7 @@
       </c>
     </row>
     <row r="219" spans="1:8" ht="18" customHeight="1">
-      <c r="A219" s="44" t="s">
+      <c r="A219" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B219" s="2" t="s">
@@ -20655,7 +20655,7 @@
       </c>
     </row>
     <row r="220" spans="1:8" ht="18" customHeight="1">
-      <c r="A220" s="44" t="s">
+      <c r="A220" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B220" s="2" t="s">
@@ -20681,7 +20681,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="18" customHeight="1">
-      <c r="A221" s="44" t="s">
+      <c r="A221" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B221" s="2" t="s">
@@ -20707,7 +20707,7 @@
       </c>
     </row>
     <row r="222" spans="1:8" ht="18" customHeight="1">
-      <c r="A222" s="44" t="s">
+      <c r="A222" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B222" s="2" t="s">
@@ -20733,7 +20733,7 @@
       </c>
     </row>
     <row r="223" spans="1:8" ht="18" customHeight="1">
-      <c r="A223" s="44" t="s">
+      <c r="A223" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B223" s="2" t="s">
@@ -20759,7 +20759,7 @@
       </c>
     </row>
     <row r="224" spans="1:8" ht="18" customHeight="1">
-      <c r="A224" s="44" t="s">
+      <c r="A224" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B224" s="2" t="s">
@@ -20785,7 +20785,7 @@
       </c>
     </row>
     <row r="225" spans="1:8" ht="18" customHeight="1">
-      <c r="A225" s="44" t="s">
+      <c r="A225" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B225" s="2" t="s">
@@ -20811,7 +20811,7 @@
       </c>
     </row>
     <row r="226" spans="1:8" ht="18" customHeight="1">
-      <c r="A226" s="44" t="s">
+      <c r="A226" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B226" s="2" t="s">
@@ -20837,7 +20837,7 @@
       </c>
     </row>
     <row r="227" spans="1:8" ht="18" customHeight="1">
-      <c r="A227" s="44" t="s">
+      <c r="A227" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B227" s="2" t="s">
@@ -20863,7 +20863,7 @@
       </c>
     </row>
     <row r="228" spans="1:8" ht="18" customHeight="1">
-      <c r="A228" s="44" t="s">
+      <c r="A228" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B228" s="2" t="s">
@@ -20889,7 +20889,7 @@
       </c>
     </row>
     <row r="229" spans="1:8" ht="18" customHeight="1">
-      <c r="A229" s="44" t="s">
+      <c r="A229" s="38" t="s">
         <v>1430</v>
       </c>
       <c r="B229" s="2" t="s">
@@ -20915,7 +20915,7 @@
       </c>
     </row>
     <row r="230" spans="1:8" ht="18" customHeight="1">
-      <c r="A230" s="45" t="s">
+      <c r="A230" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B230" s="36" t="s">
@@ -20941,7 +20941,7 @@
       </c>
     </row>
     <row r="231" spans="1:8" ht="18" customHeight="1">
-      <c r="A231" s="45" t="s">
+      <c r="A231" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B231" s="2" t="s">
@@ -20967,7 +20967,7 @@
       </c>
     </row>
     <row r="232" spans="1:8" ht="18" customHeight="1">
-      <c r="A232" s="45" t="s">
+      <c r="A232" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B232" s="2" t="s">
@@ -20993,7 +20993,7 @@
       </c>
     </row>
     <row r="233" spans="1:8" ht="18" customHeight="1">
-      <c r="A233" s="45" t="s">
+      <c r="A233" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B233" s="2" t="s">
@@ -21019,7 +21019,7 @@
       </c>
     </row>
     <row r="234" spans="1:8" ht="18" customHeight="1">
-      <c r="A234" s="45" t="s">
+      <c r="A234" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B234" s="2" t="s">
@@ -21045,7 +21045,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="18" customHeight="1">
-      <c r="A235" s="45" t="s">
+      <c r="A235" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B235" s="2" t="s">
@@ -21071,7 +21071,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="18" customHeight="1">
-      <c r="A236" s="45" t="s">
+      <c r="A236" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B236" s="2" t="s">
@@ -21097,7 +21097,7 @@
       </c>
     </row>
     <row r="237" spans="1:8" ht="18" customHeight="1">
-      <c r="A237" s="45" t="s">
+      <c r="A237" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B237" s="2" t="s">
@@ -21123,7 +21123,7 @@
       </c>
     </row>
     <row r="238" spans="1:8" ht="18" customHeight="1">
-      <c r="A238" s="45" t="s">
+      <c r="A238" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B238" s="2" t="s">
@@ -21149,7 +21149,7 @@
       </c>
     </row>
     <row r="239" spans="1:8" ht="18" customHeight="1">
-      <c r="A239" s="45" t="s">
+      <c r="A239" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B239" s="2" t="s">
@@ -21175,7 +21175,7 @@
       </c>
     </row>
     <row r="240" spans="1:8" ht="18" customHeight="1">
-      <c r="A240" s="45" t="s">
+      <c r="A240" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B240" s="2" t="s">
@@ -21201,7 +21201,7 @@
       </c>
     </row>
     <row r="241" spans="1:8" ht="18" customHeight="1">
-      <c r="A241" s="45" t="s">
+      <c r="A241" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B241" s="2" t="s">
@@ -21227,7 +21227,7 @@
       </c>
     </row>
     <row r="242" spans="1:8" ht="18" customHeight="1">
-      <c r="A242" s="45" t="s">
+      <c r="A242" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B242" s="2" t="s">
@@ -21253,7 +21253,7 @@
       </c>
     </row>
     <row r="243" spans="1:8" ht="18" customHeight="1">
-      <c r="A243" s="45" t="s">
+      <c r="A243" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B243" s="2" t="s">
@@ -21279,7 +21279,7 @@
       </c>
     </row>
     <row r="244" spans="1:8" ht="18" customHeight="1">
-      <c r="A244" s="45" t="s">
+      <c r="A244" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B244" s="2" t="s">
@@ -21305,7 +21305,7 @@
       </c>
     </row>
     <row r="245" spans="1:8" ht="18" customHeight="1">
-      <c r="A245" s="45" t="s">
+      <c r="A245" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B245" s="2" t="s">
@@ -21331,7 +21331,7 @@
       </c>
     </row>
     <row r="246" spans="1:8" ht="18" customHeight="1">
-      <c r="A246" s="45" t="s">
+      <c r="A246" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B246" s="2" t="s">
@@ -21357,7 +21357,7 @@
       </c>
     </row>
     <row r="247" spans="1:8" ht="18" customHeight="1">
-      <c r="A247" s="45" t="s">
+      <c r="A247" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B247" s="2" t="s">
@@ -21383,7 +21383,7 @@
       </c>
     </row>
     <row r="248" spans="1:8" ht="18" customHeight="1">
-      <c r="A248" s="45" t="s">
+      <c r="A248" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B248" s="2" t="s">
@@ -21409,7 +21409,7 @@
       </c>
     </row>
     <row r="249" spans="1:8" ht="18" customHeight="1">
-      <c r="A249" s="45" t="s">
+      <c r="A249" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B249" s="2" t="s">
@@ -21435,7 +21435,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="18" customHeight="1">
-      <c r="A250" s="45" t="s">
+      <c r="A250" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B250" s="2" t="s">
@@ -21461,7 +21461,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="18" customHeight="1">
-      <c r="A251" s="45" t="s">
+      <c r="A251" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B251" s="2" t="s">
@@ -21487,7 +21487,7 @@
       </c>
     </row>
     <row r="252" spans="1:8" ht="18" customHeight="1">
-      <c r="A252" s="45" t="s">
+      <c r="A252" s="39" t="s">
         <v>1432</v>
       </c>
       <c r="B252" s="20" t="s">
@@ -21513,10 +21513,10 @@
       </c>
     </row>
     <row r="253" spans="1:8" ht="18" customHeight="1">
-      <c r="A253" s="45" t="s">
+      <c r="A253" s="39" t="s">
         <v>1189</v>
       </c>
-      <c r="B253" s="46" t="s">
+      <c r="B253" s="40" t="s">
         <v>1433</v>
       </c>
       <c r="C253" s="7" t="s">
@@ -21539,7 +21539,7 @@
       </c>
     </row>
     <row r="254" spans="1:8" ht="18" customHeight="1">
-      <c r="A254" s="45" t="s">
+      <c r="A254" s="39" t="s">
         <v>1189</v>
       </c>
       <c r="B254" s="2" t="s">
@@ -21565,7 +21565,7 @@
       </c>
     </row>
     <row r="255" spans="1:8" ht="18" customHeight="1">
-      <c r="A255" s="45" t="s">
+      <c r="A255" s="39" t="s">
         <v>1189</v>
       </c>
       <c r="B255" s="2" t="s">
@@ -21591,7 +21591,7 @@
       </c>
     </row>
     <row r="256" spans="1:8" ht="18" customHeight="1">
-      <c r="A256" s="45" t="s">
+      <c r="A256" s="39" t="s">
         <v>1189</v>
       </c>
       <c r="B256" s="2" t="s">
@@ -21617,7 +21617,7 @@
       </c>
     </row>
     <row r="257" spans="1:8" ht="18" customHeight="1">
-      <c r="A257" s="45" t="s">
+      <c r="A257" s="39" t="s">
         <v>1189</v>
       </c>
       <c r="B257" s="20" t="s">
@@ -21643,10 +21643,10 @@
       </c>
     </row>
     <row r="258" spans="1:8" ht="18" customHeight="1">
-      <c r="A258" s="48" t="s">
+      <c r="A258" s="42" t="s">
         <v>562</v>
       </c>
-      <c r="B258" s="47" t="s">
+      <c r="B258" s="41" t="s">
         <v>1434</v>
       </c>
       <c r="C258" s="7" t="s">
@@ -21669,7 +21669,7 @@
       </c>
     </row>
     <row r="259" spans="1:8" ht="18" customHeight="1">
-      <c r="A259" s="48" t="s">
+      <c r="A259" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B259" s="20" t="s">
@@ -21695,7 +21695,7 @@
       </c>
     </row>
     <row r="260" spans="1:8" ht="18" customHeight="1">
-      <c r="A260" s="48" t="s">
+      <c r="A260" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B260" s="20" t="s">
@@ -21721,7 +21721,7 @@
       </c>
     </row>
     <row r="261" spans="1:8" ht="18" customHeight="1">
-      <c r="A261" s="48" t="s">
+      <c r="A261" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B261" s="20" t="s">
@@ -21747,7 +21747,7 @@
       </c>
     </row>
     <row r="262" spans="1:8" ht="18" customHeight="1">
-      <c r="A262" s="48" t="s">
+      <c r="A262" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B262" s="20" t="s">
@@ -21773,7 +21773,7 @@
       </c>
     </row>
     <row r="263" spans="1:8" ht="18" customHeight="1">
-      <c r="A263" s="48" t="s">
+      <c r="A263" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B263" s="20" t="s">
@@ -21799,7 +21799,7 @@
       </c>
     </row>
     <row r="264" spans="1:8" ht="18" customHeight="1">
-      <c r="A264" s="48" t="s">
+      <c r="A264" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B264" s="20" t="s">
@@ -21825,7 +21825,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="18" customHeight="1">
-      <c r="A265" s="48" t="s">
+      <c r="A265" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B265" s="20" t="s">
@@ -21851,7 +21851,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="18" customHeight="1">
-      <c r="A266" s="48" t="s">
+      <c r="A266" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B266" s="20" t="s">
@@ -21877,7 +21877,7 @@
       </c>
     </row>
     <row r="267" spans="1:8" ht="18" customHeight="1">
-      <c r="A267" s="48" t="s">
+      <c r="A267" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B267" s="20" t="s">
@@ -21903,7 +21903,7 @@
       </c>
     </row>
     <row r="268" spans="1:8" ht="18" customHeight="1">
-      <c r="A268" s="48" t="s">
+      <c r="A268" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B268" s="20" t="s">
@@ -21929,7 +21929,7 @@
       </c>
     </row>
     <row r="269" spans="1:8" ht="18" customHeight="1">
-      <c r="A269" s="48" t="s">
+      <c r="A269" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B269" s="20" t="s">
@@ -21955,7 +21955,7 @@
       </c>
     </row>
     <row r="270" spans="1:8" ht="18" customHeight="1">
-      <c r="A270" s="48" t="s">
+      <c r="A270" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B270" s="20" t="s">
@@ -21981,7 +21981,7 @@
       </c>
     </row>
     <row r="271" spans="1:8" ht="18" customHeight="1">
-      <c r="A271" s="48" t="s">
+      <c r="A271" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B271" s="20" t="s">
@@ -22007,7 +22007,7 @@
       </c>
     </row>
     <row r="272" spans="1:8" ht="18" customHeight="1">
-      <c r="A272" s="48" t="s">
+      <c r="A272" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B272" s="20" t="s">
@@ -22033,7 +22033,7 @@
       </c>
     </row>
     <row r="273" spans="1:8" ht="18" customHeight="1">
-      <c r="A273" s="48" t="s">
+      <c r="A273" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B273" s="20" t="s">
@@ -22059,7 +22059,7 @@
       </c>
     </row>
     <row r="274" spans="1:8" ht="18" customHeight="1">
-      <c r="A274" s="48" t="s">
+      <c r="A274" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B274" s="20" t="s">
@@ -22085,7 +22085,7 @@
       </c>
     </row>
     <row r="275" spans="1:8" ht="18" customHeight="1">
-      <c r="A275" s="48" t="s">
+      <c r="A275" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B275" s="20" t="s">
@@ -22111,7 +22111,7 @@
       </c>
     </row>
     <row r="276" spans="1:8" ht="18" customHeight="1">
-      <c r="A276" s="48" t="s">
+      <c r="A276" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B276" s="20" t="s">
@@ -22137,7 +22137,7 @@
       </c>
     </row>
     <row r="277" spans="1:8" ht="18" customHeight="1">
-      <c r="A277" s="48" t="s">
+      <c r="A277" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B277" s="20" t="s">
@@ -22163,7 +22163,7 @@
       </c>
     </row>
     <row r="278" spans="1:8" ht="18" customHeight="1">
-      <c r="A278" s="48" t="s">
+      <c r="A278" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B278" s="20" t="s">
@@ -22189,7 +22189,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="18" customHeight="1">
-      <c r="A279" s="48" t="s">
+      <c r="A279" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B279" s="20" t="s">
@@ -22215,7 +22215,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="18" customHeight="1">
-      <c r="A280" s="48" t="s">
+      <c r="A280" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B280" s="20" t="s">
@@ -22241,7 +22241,7 @@
       </c>
     </row>
     <row r="281" spans="1:8" ht="18" customHeight="1">
-      <c r="A281" s="48" t="s">
+      <c r="A281" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B281" s="20" t="s">
@@ -22267,7 +22267,7 @@
       </c>
     </row>
     <row r="282" spans="1:8" ht="18" customHeight="1">
-      <c r="A282" s="48" t="s">
+      <c r="A282" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B282" s="20" t="s">
@@ -22293,7 +22293,7 @@
       </c>
     </row>
     <row r="283" spans="1:8" ht="18" customHeight="1">
-      <c r="A283" s="48" t="s">
+      <c r="A283" s="42" t="s">
         <v>562</v>
       </c>
       <c r="B283" s="20" t="s">
@@ -22319,10 +22319,10 @@
       </c>
     </row>
     <row r="284" spans="1:8" ht="18" customHeight="1">
-      <c r="A284" s="45" t="s">
+      <c r="A284" s="39" t="s">
         <v>1436</v>
       </c>
-      <c r="B284" s="46" t="s">
+      <c r="B284" s="40" t="s">
         <v>1435</v>
       </c>
       <c r="C284" s="7" t="s">
@@ -22345,7 +22345,7 @@
       </c>
     </row>
     <row r="285" spans="1:8" ht="18" customHeight="1">
-      <c r="A285" s="45" t="s">
+      <c r="A285" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B285" s="2" t="s">
@@ -22371,7 +22371,7 @@
       </c>
     </row>
     <row r="286" spans="1:8" ht="18" customHeight="1">
-      <c r="A286" s="45" t="s">
+      <c r="A286" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B286" s="2" t="s">
@@ -22397,7 +22397,7 @@
       </c>
     </row>
     <row r="287" spans="1:8" ht="18" customHeight="1">
-      <c r="A287" s="45" t="s">
+      <c r="A287" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B287" s="2" t="s">
@@ -22423,7 +22423,7 @@
       </c>
     </row>
     <row r="288" spans="1:8" ht="18" customHeight="1">
-      <c r="A288" s="45" t="s">
+      <c r="A288" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B288" s="2" t="s">
@@ -22449,7 +22449,7 @@
       </c>
     </row>
     <row r="289" spans="1:8" ht="18" customHeight="1">
-      <c r="A289" s="45" t="s">
+      <c r="A289" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B289" s="2" t="s">
@@ -22475,7 +22475,7 @@
       </c>
     </row>
     <row r="290" spans="1:8" ht="18" customHeight="1">
-      <c r="A290" s="45" t="s">
+      <c r="A290" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B290" s="2" t="s">
@@ -22501,7 +22501,7 @@
       </c>
     </row>
     <row r="291" spans="1:8" ht="18" customHeight="1">
-      <c r="A291" s="45" t="s">
+      <c r="A291" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B291" s="2" t="s">
@@ -22527,7 +22527,7 @@
       </c>
     </row>
     <row r="292" spans="1:8" ht="18" customHeight="1">
-      <c r="A292" s="45" t="s">
+      <c r="A292" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B292" s="2" t="s">
@@ -22553,7 +22553,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="18" customHeight="1">
-      <c r="A293" s="45" t="s">
+      <c r="A293" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B293" s="2" t="s">
@@ -22579,7 +22579,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="18" customHeight="1">
-      <c r="A294" s="45" t="s">
+      <c r="A294" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B294" s="2" t="s">
@@ -22605,7 +22605,7 @@
       </c>
     </row>
     <row r="295" spans="1:8" ht="18" customHeight="1">
-      <c r="A295" s="45" t="s">
+      <c r="A295" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B295" s="2" t="s">
@@ -22631,7 +22631,7 @@
       </c>
     </row>
     <row r="296" spans="1:8" ht="18" customHeight="1">
-      <c r="A296" s="45" t="s">
+      <c r="A296" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B296" s="2" t="s">
@@ -22657,7 +22657,7 @@
       </c>
     </row>
     <row r="297" spans="1:8" ht="18" customHeight="1">
-      <c r="A297" s="45" t="s">
+      <c r="A297" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B297" s="2" t="s">
@@ -22683,7 +22683,7 @@
       </c>
     </row>
     <row r="298" spans="1:8" ht="18" customHeight="1">
-      <c r="A298" s="45" t="s">
+      <c r="A298" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B298" s="2" t="s">
@@ -22709,7 +22709,7 @@
       </c>
     </row>
     <row r="299" spans="1:8" ht="18" customHeight="1">
-      <c r="A299" s="45" t="s">
+      <c r="A299" s="39" t="s">
         <v>1436</v>
       </c>
       <c r="B299" s="2" t="s">
@@ -23959,7 +23959,7 @@
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="46" t="s">
+      <c r="A47" s="40" t="s">
         <v>1438</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -23985,7 +23985,7 @@
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="46" t="s">
+      <c r="A48" s="40" t="s">
         <v>1438</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -24011,7 +24011,7 @@
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="46" t="s">
+      <c r="A49" s="40" t="s">
         <v>1438</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -24037,7 +24037,7 @@
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="46" t="s">
+      <c r="A50" s="40" t="s">
         <v>1438</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -24063,7 +24063,7 @@
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="40" t="s">
         <v>1438</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -24089,7 +24089,7 @@
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="46" t="s">
+      <c r="A52" s="40" t="s">
         <v>1438</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -24115,7 +24115,7 @@
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="46" t="s">
+      <c r="A53" s="40" t="s">
         <v>1438</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -24141,7 +24141,7 @@
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="46" t="s">
+      <c r="A54" s="40" t="s">
         <v>1437</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -24167,7 +24167,7 @@
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="46" t="s">
+      <c r="A55" s="40" t="s">
         <v>1437</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -24193,7 +24193,7 @@
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="46" t="s">
+      <c r="A56" s="40" t="s">
         <v>1437</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -24219,7 +24219,7 @@
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="46" t="s">
+      <c r="A57" s="40" t="s">
         <v>1437</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -24245,7 +24245,7 @@
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="46" t="s">
+      <c r="A58" s="40" t="s">
         <v>1437</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -24271,7 +24271,7 @@
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="46" t="s">
+      <c r="A59" s="40" t="s">
         <v>1437</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -24297,7 +24297,7 @@
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="46" t="s">
+      <c r="A60" s="40" t="s">
         <v>1437</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -24323,7 +24323,7 @@
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="46" t="s">
+      <c r="A61" s="40" t="s">
         <v>1437</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -24401,10 +24401,10 @@
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="46" t="s">
+      <c r="A64" s="40" t="s">
         <v>1439</v>
       </c>
-      <c r="B64" s="46" t="s">
+      <c r="B64" s="40" t="s">
         <v>1439</v>
       </c>
       <c r="C64" s="7" t="s">
@@ -24947,10 +24947,10 @@
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="46" t="s">
+      <c r="A85" s="40" t="s">
         <v>1440</v>
       </c>
-      <c r="B85" s="46" t="s">
+      <c r="B85" s="40" t="s">
         <v>1440</v>
       </c>
       <c r="C85" s="7" t="s">
@@ -25207,10 +25207,10 @@
       </c>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="45" t="s">
+      <c r="A95" s="39" t="s">
         <v>558</v>
       </c>
-      <c r="B95" s="49" t="s">
+      <c r="B95" s="43" t="s">
         <v>559</v>
       </c>
       <c r="C95" s="7" t="s">
@@ -25233,7 +25233,7 @@
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="45" t="s">
+      <c r="A96" s="39" t="s">
         <v>558</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -25259,7 +25259,7 @@
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="45" t="s">
+      <c r="A97" s="39" t="s">
         <v>558</v>
       </c>
       <c r="B97" s="12" t="s">
@@ -25285,10 +25285,10 @@
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="45" t="s">
+      <c r="A98" s="39" t="s">
         <v>1442</v>
       </c>
-      <c r="B98" s="50" t="s">
+      <c r="B98" s="44" t="s">
         <v>1441</v>
       </c>
       <c r="C98" s="7" t="s">
@@ -25311,7 +25311,7 @@
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="45" t="s">
+      <c r="A99" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B99" s="12" t="s">
@@ -25337,7 +25337,7 @@
       </c>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="45" t="s">
+      <c r="A100" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B100" s="30" t="s">
@@ -25363,7 +25363,7 @@
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="45" t="s">
+      <c r="A101" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -25389,7 +25389,7 @@
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="45" t="s">
+      <c r="A102" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -25415,7 +25415,7 @@
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="45" t="s">
+      <c r="A103" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -25441,7 +25441,7 @@
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="45" t="s">
+      <c r="A104" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -25467,7 +25467,7 @@
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="45" t="s">
+      <c r="A105" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -25493,7 +25493,7 @@
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="45" t="s">
+      <c r="A106" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -25519,7 +25519,7 @@
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="45" t="s">
+      <c r="A107" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -25545,7 +25545,7 @@
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="45" t="s">
+      <c r="A108" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -25571,7 +25571,7 @@
       </c>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="45" t="s">
+      <c r="A109" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -25597,7 +25597,7 @@
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="45" t="s">
+      <c r="A110" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -25623,7 +25623,7 @@
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="45" t="s">
+      <c r="A111" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -25649,7 +25649,7 @@
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="45" t="s">
+      <c r="A112" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -25675,7 +25675,7 @@
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="45" t="s">
+      <c r="A113" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -25701,7 +25701,7 @@
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="45" t="s">
+      <c r="A114" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -25727,7 +25727,7 @@
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="45" t="s">
+      <c r="A115" s="39" t="s">
         <v>1442</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -27728,7 +27728,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="45" t="s">
         <v>295</v>
       </c>
       <c r="C2" s="31" t="s">
@@ -27742,7 +27742,7 @@
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="38"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="31" t="s">
         <v>1031</v>
       </c>
@@ -27754,7 +27754,7 @@
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="38"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="31" t="s">
         <v>297</v>
       </c>
@@ -27766,7 +27766,7 @@
       </c>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="38"/>
+      <c r="B5" s="45"/>
       <c r="C5" s="31" t="s">
         <v>298</v>
       </c>
@@ -27778,7 +27778,7 @@
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="38"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="31" t="s">
         <v>299</v>
       </c>
@@ -27790,7 +27790,7 @@
       </c>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="38"/>
+      <c r="B7" s="45"/>
       <c r="C7" s="31" t="s">
         <v>300</v>
       </c>
@@ -27802,7 +27802,7 @@
       </c>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="38"/>
+      <c r="B8" s="45"/>
       <c r="C8" s="31" t="s">
         <v>301</v>
       </c>
@@ -27814,7 +27814,7 @@
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="38"/>
+      <c r="B9" s="45"/>
       <c r="C9" s="31" t="s">
         <v>302</v>
       </c>
@@ -27826,7 +27826,7 @@
       </c>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="38"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="31" t="s">
         <v>303</v>
       </c>
@@ -27838,7 +27838,7 @@
       </c>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="38"/>
+      <c r="B11" s="45"/>
       <c r="C11" s="31" t="s">
         <v>304</v>
       </c>
@@ -27850,7 +27850,7 @@
       </c>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="38"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="31" t="s">
         <v>305</v>
       </c>
@@ -27862,7 +27862,7 @@
       </c>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="38"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="31" t="s">
         <v>306</v>
       </c>
@@ -27874,7 +27874,7 @@
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="38"/>
+      <c r="B14" s="45"/>
       <c r="C14" s="31" t="s">
         <v>307</v>
       </c>
@@ -27886,7 +27886,7 @@
       </c>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="38"/>
+      <c r="B15" s="45"/>
       <c r="C15" s="31" t="s">
         <v>308</v>
       </c>
@@ -27898,7 +27898,7 @@
       </c>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="38"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="31" t="s">
         <v>309</v>
       </c>
@@ -27910,7 +27910,7 @@
       </c>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="38"/>
+      <c r="B17" s="45"/>
       <c r="C17" s="31" t="s">
         <v>310</v>
       </c>
@@ -27922,7 +27922,7 @@
       </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="38"/>
+      <c r="B18" s="45"/>
       <c r="C18" s="31" t="s">
         <v>311</v>
       </c>
@@ -27934,7 +27934,7 @@
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="38"/>
+      <c r="B19" s="45"/>
       <c r="C19" s="31" t="s">
         <v>312</v>
       </c>
@@ -27946,7 +27946,7 @@
       </c>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="38"/>
+      <c r="B20" s="45"/>
       <c r="C20" s="31" t="s">
         <v>313</v>
       </c>
@@ -27958,7 +27958,7 @@
       </c>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="47" t="s">
         <v>314</v>
       </c>
       <c r="C21" s="31" t="s">
@@ -27972,7 +27972,7 @@
       </c>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="38"/>
+      <c r="B22" s="45"/>
       <c r="C22" s="31" t="s">
         <v>316</v>
       </c>
@@ -27984,7 +27984,7 @@
       </c>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="38"/>
+      <c r="B23" s="45"/>
       <c r="C23" s="31" t="s">
         <v>317</v>
       </c>
@@ -27996,7 +27996,7 @@
       </c>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="38"/>
+      <c r="B24" s="45"/>
       <c r="C24" s="31" t="s">
         <v>318</v>
       </c>
@@ -28008,7 +28008,7 @@
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="47" t="s">
         <v>319</v>
       </c>
       <c r="C25" s="31" t="s">
@@ -28025,7 +28025,7 @@
       </c>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="38"/>
+      <c r="B26" s="45"/>
       <c r="C26" s="31" t="s">
         <v>321</v>
       </c>
@@ -28040,7 +28040,7 @@
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="38"/>
+      <c r="B27" s="45"/>
       <c r="C27" s="31" t="s">
         <v>322</v>
       </c>
@@ -28055,7 +28055,7 @@
       </c>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="38"/>
+      <c r="B28" s="45"/>
       <c r="C28" s="31" t="s">
         <v>323</v>
       </c>
@@ -28070,7 +28070,7 @@
       </c>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="38" t="s">
+      <c r="B29" s="45" t="s">
         <v>324</v>
       </c>
       <c r="C29" s="31" t="s">
@@ -28084,7 +28084,7 @@
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="38"/>
+      <c r="B30" s="45"/>
       <c r="C30" s="31" t="s">
         <v>326</v>
       </c>
@@ -28096,7 +28096,7 @@
       </c>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="38"/>
+      <c r="B31" s="45"/>
       <c r="C31" s="31" t="s">
         <v>327</v>
       </c>
@@ -28111,7 +28111,7 @@
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="38"/>
+      <c r="B32" s="45"/>
       <c r="C32" s="31" t="s">
         <v>328</v>
       </c>
@@ -28126,7 +28126,7 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="38"/>
+      <c r="B33" s="45"/>
       <c r="C33" s="31" t="s">
         <v>329</v>
       </c>
@@ -28141,7 +28141,7 @@
       </c>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="47" t="s">
         <v>330</v>
       </c>
       <c r="C34" s="31" t="s">
@@ -28155,7 +28155,7 @@
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="39"/>
+      <c r="B35" s="47"/>
       <c r="C35" s="31" t="s">
         <v>332</v>
       </c>
@@ -28167,7 +28167,7 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="39"/>
+      <c r="B36" s="47"/>
       <c r="C36" s="31" t="s">
         <v>333</v>
       </c>
@@ -28179,7 +28179,7 @@
       </c>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="39"/>
+      <c r="B37" s="47"/>
       <c r="C37" s="31" t="s">
         <v>334</v>
       </c>
@@ -28191,7 +28191,7 @@
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="38" t="s">
+      <c r="B38" s="45" t="s">
         <v>335</v>
       </c>
       <c r="C38" s="31" t="s">
@@ -28205,7 +28205,7 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="38"/>
+      <c r="B39" s="45"/>
       <c r="C39" s="31" t="s">
         <v>337</v>
       </c>
@@ -28217,7 +28217,7 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="38"/>
+      <c r="B40" s="45"/>
       <c r="C40" s="31" t="s">
         <v>338</v>
       </c>
@@ -28229,7 +28229,7 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="38"/>
+      <c r="B41" s="45"/>
       <c r="C41" s="31" t="s">
         <v>339</v>
       </c>
@@ -28241,7 +28241,7 @@
       </c>
     </row>
     <row r="42" spans="2:6">
-      <c r="B42" s="38"/>
+      <c r="B42" s="45"/>
       <c r="C42" s="31" t="s">
         <v>340</v>
       </c>
@@ -28253,7 +28253,7 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="38"/>
+      <c r="B43" s="45"/>
       <c r="C43" s="31" t="s">
         <v>341</v>
       </c>
@@ -28265,7 +28265,7 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="38"/>
+      <c r="B44" s="45"/>
       <c r="C44" s="31" t="s">
         <v>342</v>
       </c>
@@ -28277,7 +28277,7 @@
       </c>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="38"/>
+      <c r="B45" s="45"/>
       <c r="C45" s="31" t="s">
         <v>343</v>
       </c>
@@ -28289,7 +28289,7 @@
       </c>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="38"/>
+      <c r="B46" s="45"/>
       <c r="C46" s="31" t="s">
         <v>344</v>
       </c>
@@ -28301,7 +28301,7 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="39" t="s">
+      <c r="B47" s="47" t="s">
         <v>345</v>
       </c>
       <c r="C47" s="31" t="s">
@@ -28315,7 +28315,7 @@
       </c>
     </row>
     <row r="48" spans="2:6">
-      <c r="B48" s="38"/>
+      <c r="B48" s="45"/>
       <c r="C48" s="31" t="s">
         <v>347</v>
       </c>
@@ -28327,7 +28327,7 @@
       </c>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="38"/>
+      <c r="B49" s="45"/>
       <c r="C49" s="31" t="s">
         <v>348</v>
       </c>
@@ -28339,7 +28339,7 @@
       </c>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="38"/>
+      <c r="B50" s="45"/>
       <c r="C50" s="31" t="s">
         <v>349</v>
       </c>
@@ -28351,7 +28351,7 @@
       </c>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="38"/>
+      <c r="B51" s="45"/>
       <c r="C51" s="31" t="s">
         <v>350</v>
       </c>
@@ -28363,7 +28363,7 @@
       </c>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="38"/>
+      <c r="B52" s="45"/>
       <c r="C52" s="31" t="s">
         <v>351</v>
       </c>
@@ -28375,7 +28375,7 @@
       </c>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="38"/>
+      <c r="B53" s="45"/>
       <c r="C53" s="31" t="s">
         <v>352</v>
       </c>
@@ -28387,7 +28387,7 @@
       </c>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="39" t="s">
+      <c r="B54" s="47" t="s">
         <v>353</v>
       </c>
       <c r="C54" s="31" t="s">
@@ -28401,7 +28401,7 @@
       </c>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="38"/>
+      <c r="B55" s="45"/>
       <c r="C55" s="31" t="s">
         <v>1252</v>
       </c>
@@ -28413,7 +28413,7 @@
       </c>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="38"/>
+      <c r="B56" s="45"/>
       <c r="C56" s="31" t="s">
         <v>355</v>
       </c>
@@ -28425,7 +28425,7 @@
       </c>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="38"/>
+      <c r="B57" s="45"/>
       <c r="C57" s="31" t="s">
         <v>356</v>
       </c>
@@ -28437,7 +28437,7 @@
       </c>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="38"/>
+      <c r="B58" s="45"/>
       <c r="C58" s="31" t="s">
         <v>357</v>
       </c>
@@ -28449,7 +28449,7 @@
       </c>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="38"/>
+      <c r="B59" s="45"/>
       <c r="C59" s="31" t="s">
         <v>358</v>
       </c>
@@ -28461,7 +28461,7 @@
       </c>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="38"/>
+      <c r="B60" s="45"/>
       <c r="C60" s="31" t="s">
         <v>359</v>
       </c>
@@ -28473,7 +28473,7 @@
       </c>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="38"/>
+      <c r="B61" s="45"/>
       <c r="C61" s="31" t="s">
         <v>360</v>
       </c>
@@ -28485,7 +28485,7 @@
       </c>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="39" t="s">
+      <c r="B62" s="47" t="s">
         <v>361</v>
       </c>
       <c r="C62" s="31" t="s">
@@ -28499,7 +28499,7 @@
       </c>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="38"/>
+      <c r="B63" s="45"/>
       <c r="C63" s="31" t="s">
         <v>363</v>
       </c>
@@ -28511,7 +28511,7 @@
       </c>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="38"/>
+      <c r="B64" s="45"/>
       <c r="C64" s="31" t="s">
         <v>364</v>
       </c>
@@ -28523,7 +28523,7 @@
       </c>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="38"/>
+      <c r="B65" s="45"/>
       <c r="C65" s="31" t="s">
         <v>365</v>
       </c>
@@ -28535,7 +28535,7 @@
       </c>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="38"/>
+      <c r="B66" s="45"/>
       <c r="C66" s="31" t="s">
         <v>366</v>
       </c>
@@ -28547,7 +28547,7 @@
       </c>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="39" t="s">
+      <c r="B67" s="47" t="s">
         <v>367</v>
       </c>
       <c r="C67" s="31" t="s">
@@ -28561,7 +28561,7 @@
       </c>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="39"/>
+      <c r="B68" s="47"/>
       <c r="C68" s="31" t="s">
         <v>368</v>
       </c>
@@ -28573,7 +28573,7 @@
       </c>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="39"/>
+      <c r="B69" s="47"/>
       <c r="C69" s="31" t="s">
         <v>369</v>
       </c>
@@ -28585,7 +28585,7 @@
       </c>
     </row>
     <row r="70" spans="2:5">
-      <c r="B70" s="39"/>
+      <c r="B70" s="47"/>
       <c r="C70" s="31" t="s">
         <v>370</v>
       </c>
@@ -28597,7 +28597,7 @@
       </c>
     </row>
     <row r="71" spans="2:5">
-      <c r="B71" s="39"/>
+      <c r="B71" s="47"/>
       <c r="C71" s="31" t="s">
         <v>371</v>
       </c>
@@ -28609,7 +28609,7 @@
       </c>
     </row>
     <row r="72" spans="2:5">
-      <c r="B72" s="39"/>
+      <c r="B72" s="47"/>
       <c r="C72" s="31" t="s">
         <v>372</v>
       </c>
@@ -28621,7 +28621,7 @@
       </c>
     </row>
     <row r="73" spans="2:5">
-      <c r="B73" s="39"/>
+      <c r="B73" s="47"/>
       <c r="C73" s="31" t="s">
         <v>373</v>
       </c>
@@ -28633,7 +28633,7 @@
       </c>
     </row>
     <row r="74" spans="2:5">
-      <c r="B74" s="39"/>
+      <c r="B74" s="47"/>
       <c r="C74" s="31" t="s">
         <v>374</v>
       </c>
@@ -28645,7 +28645,7 @@
       </c>
     </row>
     <row r="75" spans="2:5">
-      <c r="B75" s="39"/>
+      <c r="B75" s="47"/>
       <c r="C75" s="31" t="s">
         <v>375</v>
       </c>
@@ -28657,7 +28657,7 @@
       </c>
     </row>
     <row r="76" spans="2:5">
-      <c r="B76" s="39"/>
+      <c r="B76" s="47"/>
       <c r="C76" s="31" t="s">
         <v>376</v>
       </c>
@@ -28669,7 +28669,7 @@
       </c>
     </row>
     <row r="77" spans="2:5">
-      <c r="B77" s="39"/>
+      <c r="B77" s="47"/>
       <c r="C77" s="31" t="s">
         <v>377</v>
       </c>
@@ -28681,7 +28681,7 @@
       </c>
     </row>
     <row r="78" spans="2:5">
-      <c r="B78" s="39"/>
+      <c r="B78" s="47"/>
       <c r="C78" s="31" t="s">
         <v>378</v>
       </c>
@@ -28693,7 +28693,7 @@
       </c>
     </row>
     <row r="79" spans="2:5">
-      <c r="B79" s="38" t="s">
+      <c r="B79" s="45" t="s">
         <v>379</v>
       </c>
       <c r="C79" s="31" t="s">
@@ -28707,7 +28707,7 @@
       </c>
     </row>
     <row r="80" spans="2:5">
-      <c r="B80" s="38"/>
+      <c r="B80" s="45"/>
       <c r="C80" s="31" t="s">
         <v>381</v>
       </c>
@@ -28719,7 +28719,7 @@
       </c>
     </row>
     <row r="81" spans="2:5">
-      <c r="B81" s="38"/>
+      <c r="B81" s="45"/>
       <c r="C81" s="31" t="s">
         <v>382</v>
       </c>
@@ -28731,7 +28731,7 @@
       </c>
     </row>
     <row r="82" spans="2:5">
-      <c r="B82" s="38"/>
+      <c r="B82" s="45"/>
       <c r="C82" s="31" t="s">
         <v>383</v>
       </c>
@@ -28743,7 +28743,7 @@
       </c>
     </row>
     <row r="83" spans="2:5">
-      <c r="B83" s="38"/>
+      <c r="B83" s="45"/>
       <c r="C83" s="31" t="s">
         <v>384</v>
       </c>
@@ -28755,7 +28755,7 @@
       </c>
     </row>
     <row r="84" spans="2:5">
-      <c r="B84" s="38"/>
+      <c r="B84" s="45"/>
       <c r="C84" s="31" t="s">
         <v>385</v>
       </c>
@@ -28767,7 +28767,7 @@
       </c>
     </row>
     <row r="85" spans="2:5">
-      <c r="B85" s="38" t="s">
+      <c r="B85" s="45" t="s">
         <v>386</v>
       </c>
       <c r="C85" s="31" t="s">
@@ -28781,7 +28781,7 @@
       </c>
     </row>
     <row r="86" spans="2:5">
-      <c r="B86" s="38"/>
+      <c r="B86" s="45"/>
       <c r="C86" s="31" t="s">
         <v>388</v>
       </c>
@@ -28793,7 +28793,7 @@
       </c>
     </row>
     <row r="87" spans="2:5">
-      <c r="B87" s="38"/>
+      <c r="B87" s="45"/>
       <c r="C87" s="31" t="s">
         <v>389</v>
       </c>
@@ -28805,7 +28805,7 @@
       </c>
     </row>
     <row r="88" spans="2:5">
-      <c r="B88" s="38"/>
+      <c r="B88" s="45"/>
       <c r="C88" s="31" t="s">
         <v>390</v>
       </c>
@@ -28817,7 +28817,7 @@
       </c>
     </row>
     <row r="89" spans="2:5">
-      <c r="B89" s="38"/>
+      <c r="B89" s="45"/>
       <c r="C89" s="31" t="s">
         <v>391</v>
       </c>
@@ -28829,7 +28829,7 @@
       </c>
     </row>
     <row r="90" spans="2:5">
-      <c r="B90" s="38"/>
+      <c r="B90" s="45"/>
       <c r="C90" s="31" t="s">
         <v>392</v>
       </c>
@@ -28841,7 +28841,7 @@
       </c>
     </row>
     <row r="91" spans="2:5">
-      <c r="B91" s="38" t="s">
+      <c r="B91" s="45" t="s">
         <v>393</v>
       </c>
       <c r="C91" s="31" t="s">
@@ -28855,7 +28855,7 @@
       </c>
     </row>
     <row r="92" spans="2:5">
-      <c r="B92" s="38"/>
+      <c r="B92" s="45"/>
       <c r="C92" s="31" t="s">
         <v>395</v>
       </c>
@@ -28867,7 +28867,7 @@
       </c>
     </row>
     <row r="93" spans="2:5">
-      <c r="B93" s="38"/>
+      <c r="B93" s="45"/>
       <c r="C93" s="31" t="s">
         <v>396</v>
       </c>
@@ -28879,7 +28879,7 @@
       </c>
     </row>
     <row r="94" spans="2:5">
-      <c r="B94" s="39" t="s">
+      <c r="B94" s="47" t="s">
         <v>397</v>
       </c>
       <c r="C94" s="31" t="s">
@@ -28893,7 +28893,7 @@
       </c>
     </row>
     <row r="95" spans="2:5">
-      <c r="B95" s="39"/>
+      <c r="B95" s="47"/>
       <c r="C95" s="31" t="s">
         <v>399</v>
       </c>
@@ -28905,7 +28905,7 @@
       </c>
     </row>
     <row r="96" spans="2:5">
-      <c r="B96" s="39" t="s">
+      <c r="B96" s="47" t="s">
         <v>400</v>
       </c>
       <c r="C96" s="31" t="s">
@@ -28919,7 +28919,7 @@
       </c>
     </row>
     <row r="97" spans="2:5">
-      <c r="B97" s="38"/>
+      <c r="B97" s="45"/>
       <c r="C97" s="31" t="s">
         <v>402</v>
       </c>
@@ -28931,7 +28931,7 @@
       </c>
     </row>
     <row r="98" spans="2:5">
-      <c r="B98" s="38"/>
+      <c r="B98" s="45"/>
       <c r="C98" s="31" t="s">
         <v>403</v>
       </c>
@@ -28943,7 +28943,7 @@
       </c>
     </row>
     <row r="99" spans="2:5">
-      <c r="B99" s="40" t="s">
+      <c r="B99" s="50" t="s">
         <v>404</v>
       </c>
       <c r="C99" s="33" t="s">
@@ -28957,7 +28957,7 @@
       </c>
     </row>
     <row r="100" spans="2:5">
-      <c r="B100" s="40"/>
+      <c r="B100" s="50"/>
       <c r="C100" s="33" t="s">
         <v>406</v>
       </c>
@@ -28969,7 +28969,7 @@
       </c>
     </row>
     <row r="101" spans="2:5">
-      <c r="B101" s="40"/>
+      <c r="B101" s="50"/>
       <c r="C101" s="33" t="s">
         <v>407</v>
       </c>
@@ -28981,7 +28981,7 @@
       </c>
     </row>
     <row r="102" spans="2:5">
-      <c r="B102" s="40"/>
+      <c r="B102" s="50"/>
       <c r="C102" s="33" t="s">
         <v>408</v>
       </c>
@@ -28993,7 +28993,7 @@
       </c>
     </row>
     <row r="103" spans="2:5">
-      <c r="B103" s="40"/>
+      <c r="B103" s="50"/>
       <c r="C103" s="33" t="s">
         <v>409</v>
       </c>
@@ -29005,7 +29005,7 @@
       </c>
     </row>
     <row r="104" spans="2:5">
-      <c r="B104" s="40"/>
+      <c r="B104" s="50"/>
       <c r="C104" s="33" t="s">
         <v>410</v>
       </c>
@@ -29017,7 +29017,7 @@
       </c>
     </row>
     <row r="105" spans="2:5">
-      <c r="B105" s="40"/>
+      <c r="B105" s="50"/>
       <c r="C105" s="33" t="s">
         <v>411</v>
       </c>
@@ -29029,7 +29029,7 @@
       </c>
     </row>
     <row r="106" spans="2:5">
-      <c r="B106" s="40"/>
+      <c r="B106" s="50"/>
       <c r="C106" s="33" t="s">
         <v>412</v>
       </c>
@@ -29041,7 +29041,7 @@
       </c>
     </row>
     <row r="107" spans="2:5">
-      <c r="B107" s="40"/>
+      <c r="B107" s="50"/>
       <c r="C107" s="33" t="s">
         <v>413</v>
       </c>
@@ -29053,7 +29053,7 @@
       </c>
     </row>
     <row r="108" spans="2:5">
-      <c r="B108" s="40"/>
+      <c r="B108" s="50"/>
       <c r="C108" s="33" t="s">
         <v>414</v>
       </c>
@@ -29065,7 +29065,7 @@
       </c>
     </row>
     <row r="109" spans="2:5">
-      <c r="B109" s="40"/>
+      <c r="B109" s="50"/>
       <c r="C109" s="33" t="s">
         <v>415</v>
       </c>
@@ -29077,7 +29077,7 @@
       </c>
     </row>
     <row r="110" spans="2:5">
-      <c r="B110" s="40"/>
+      <c r="B110" s="50"/>
       <c r="C110" s="33" t="s">
         <v>416</v>
       </c>
@@ -29089,7 +29089,7 @@
       </c>
     </row>
     <row r="111" spans="2:5">
-      <c r="B111" s="40"/>
+      <c r="B111" s="50"/>
       <c r="C111" s="33" t="s">
         <v>417</v>
       </c>
@@ -29101,7 +29101,7 @@
       </c>
     </row>
     <row r="112" spans="2:5">
-      <c r="B112" s="40"/>
+      <c r="B112" s="50"/>
       <c r="C112" s="33" t="s">
         <v>418</v>
       </c>
@@ -29113,7 +29113,7 @@
       </c>
     </row>
     <row r="113" spans="2:5">
-      <c r="B113" s="40"/>
+      <c r="B113" s="50"/>
       <c r="C113" s="33" t="s">
         <v>419</v>
       </c>
@@ -29125,7 +29125,7 @@
       </c>
     </row>
     <row r="114" spans="2:5">
-      <c r="B114" s="40"/>
+      <c r="B114" s="50"/>
       <c r="C114" s="33" t="s">
         <v>420</v>
       </c>
@@ -29137,7 +29137,7 @@
       </c>
     </row>
     <row r="115" spans="2:5">
-      <c r="B115" s="40"/>
+      <c r="B115" s="50"/>
       <c r="C115" s="33" t="s">
         <v>421</v>
       </c>
@@ -29149,7 +29149,7 @@
       </c>
     </row>
     <row r="116" spans="2:5">
-      <c r="B116" s="40"/>
+      <c r="B116" s="50"/>
       <c r="C116" s="33" t="s">
         <v>422</v>
       </c>
@@ -29161,7 +29161,7 @@
       </c>
     </row>
     <row r="117" spans="2:5">
-      <c r="B117" s="40"/>
+      <c r="B117" s="50"/>
       <c r="C117" s="33" t="s">
         <v>423</v>
       </c>
@@ -29173,7 +29173,7 @@
       </c>
     </row>
     <row r="118" spans="2:5">
-      <c r="B118" s="40"/>
+      <c r="B118" s="50"/>
       <c r="C118" s="33" t="s">
         <v>424</v>
       </c>
@@ -29185,7 +29185,7 @@
       </c>
     </row>
     <row r="119" spans="2:5">
-      <c r="B119" s="40"/>
+      <c r="B119" s="50"/>
       <c r="C119" s="33" t="s">
         <v>425</v>
       </c>
@@ -29197,7 +29197,7 @@
       </c>
     </row>
     <row r="120" spans="2:5">
-      <c r="B120" s="40"/>
+      <c r="B120" s="50"/>
       <c r="C120" s="33" t="s">
         <v>426</v>
       </c>
@@ -29209,7 +29209,7 @@
       </c>
     </row>
     <row r="121" spans="2:5">
-      <c r="B121" s="39" t="s">
+      <c r="B121" s="47" t="s">
         <v>427</v>
       </c>
       <c r="C121" s="31" t="s">
@@ -29223,7 +29223,7 @@
       </c>
     </row>
     <row r="122" spans="2:5">
-      <c r="B122" s="39"/>
+      <c r="B122" s="47"/>
       <c r="C122" s="31" t="s">
         <v>428</v>
       </c>
@@ -29235,7 +29235,7 @@
       </c>
     </row>
     <row r="123" spans="2:5">
-      <c r="B123" s="39"/>
+      <c r="B123" s="47"/>
       <c r="C123" s="31" t="s">
         <v>429</v>
       </c>
@@ -29247,7 +29247,7 @@
       </c>
     </row>
     <row r="124" spans="2:5">
-      <c r="B124" s="39"/>
+      <c r="B124" s="47"/>
       <c r="C124" s="31" t="s">
         <v>430</v>
       </c>
@@ -29259,7 +29259,7 @@
       </c>
     </row>
     <row r="125" spans="2:5">
-      <c r="B125" s="39"/>
+      <c r="B125" s="47"/>
       <c r="C125" s="31" t="s">
         <v>431</v>
       </c>
@@ -29271,7 +29271,7 @@
       </c>
     </row>
     <row r="126" spans="2:5">
-      <c r="B126" s="39" t="s">
+      <c r="B126" s="47" t="s">
         <v>432</v>
       </c>
       <c r="C126" s="31" t="s">
@@ -29285,7 +29285,7 @@
       </c>
     </row>
     <row r="127" spans="2:5">
-      <c r="B127" s="39"/>
+      <c r="B127" s="47"/>
       <c r="C127" s="31" t="s">
         <v>433</v>
       </c>
@@ -29297,7 +29297,7 @@
       </c>
     </row>
     <row r="128" spans="2:5">
-      <c r="B128" s="39"/>
+      <c r="B128" s="47"/>
       <c r="C128" s="31" t="s">
         <v>434</v>
       </c>
@@ -29309,7 +29309,7 @@
       </c>
     </row>
     <row r="129" spans="2:6">
-      <c r="B129" s="39"/>
+      <c r="B129" s="47"/>
       <c r="C129" s="31" t="s">
         <v>435</v>
       </c>
@@ -29321,7 +29321,7 @@
       </c>
     </row>
     <row r="130" spans="2:6">
-      <c r="B130" s="39"/>
+      <c r="B130" s="47"/>
       <c r="C130" s="31" t="s">
         <v>436</v>
       </c>
@@ -29333,7 +29333,7 @@
       </c>
     </row>
     <row r="131" spans="2:6">
-      <c r="B131" s="39" t="s">
+      <c r="B131" s="47" t="s">
         <v>437</v>
       </c>
       <c r="C131" s="31" t="s">
@@ -29347,7 +29347,7 @@
       </c>
     </row>
     <row r="132" spans="2:6">
-      <c r="B132" s="38"/>
+      <c r="B132" s="45"/>
       <c r="C132" s="31" t="s">
         <v>439</v>
       </c>
@@ -29359,7 +29359,7 @@
       </c>
     </row>
     <row r="133" spans="2:6">
-      <c r="B133" s="39" t="s">
+      <c r="B133" s="47" t="s">
         <v>440</v>
       </c>
       <c r="C133" s="31" t="s">
@@ -29373,7 +29373,7 @@
       </c>
     </row>
     <row r="134" spans="2:6">
-      <c r="B134" s="38"/>
+      <c r="B134" s="45"/>
       <c r="C134" s="31" t="s">
         <v>441</v>
       </c>
@@ -29385,7 +29385,7 @@
       </c>
     </row>
     <row r="135" spans="2:6">
-      <c r="B135" s="38"/>
+      <c r="B135" s="45"/>
       <c r="C135" s="31" t="s">
         <v>442</v>
       </c>
@@ -29397,7 +29397,7 @@
       </c>
     </row>
     <row r="136" spans="2:6">
-      <c r="B136" s="38"/>
+      <c r="B136" s="45"/>
       <c r="C136" s="31" t="s">
         <v>443</v>
       </c>
@@ -29409,7 +29409,7 @@
       </c>
     </row>
     <row r="137" spans="2:6">
-      <c r="B137" s="38"/>
+      <c r="B137" s="45"/>
       <c r="C137" s="31" t="s">
         <v>444</v>
       </c>
@@ -29421,7 +29421,7 @@
       </c>
     </row>
     <row r="138" spans="2:6">
-      <c r="B138" s="38"/>
+      <c r="B138" s="45"/>
       <c r="C138" s="31" t="s">
         <v>445</v>
       </c>
@@ -29433,7 +29433,7 @@
       </c>
     </row>
     <row r="139" spans="2:6">
-      <c r="B139" s="39" t="s">
+      <c r="B139" s="47" t="s">
         <v>446</v>
       </c>
       <c r="C139" s="31" t="s">
@@ -29447,7 +29447,7 @@
       </c>
     </row>
     <row r="140" spans="2:6">
-      <c r="B140" s="39"/>
+      <c r="B140" s="47"/>
       <c r="C140" s="31" t="s">
         <v>447</v>
       </c>
@@ -29473,7 +29473,7 @@
       </c>
     </row>
     <row r="142" spans="2:6">
-      <c r="B142" s="39" t="s">
+      <c r="B142" s="47" t="s">
         <v>449</v>
       </c>
       <c r="C142" s="31" t="s">
@@ -29490,7 +29490,7 @@
       </c>
     </row>
     <row r="143" spans="2:6">
-      <c r="B143" s="38"/>
+      <c r="B143" s="45"/>
       <c r="C143" s="31" t="s">
         <v>1268</v>
       </c>
@@ -29505,7 +29505,7 @@
       </c>
     </row>
     <row r="144" spans="2:6">
-      <c r="B144" s="39" t="s">
+      <c r="B144" s="47" t="s">
         <v>451</v>
       </c>
       <c r="C144" s="31" t="s">
@@ -29522,7 +29522,7 @@
       </c>
     </row>
     <row r="145" spans="2:7">
-      <c r="B145" s="38"/>
+      <c r="B145" s="45"/>
       <c r="C145" s="31" t="s">
         <v>452</v>
       </c>
@@ -29537,7 +29537,7 @@
       </c>
     </row>
     <row r="146" spans="2:7">
-      <c r="B146" s="39" t="s">
+      <c r="B146" s="47" t="s">
         <v>453</v>
       </c>
       <c r="C146" s="31" t="s">
@@ -29554,7 +29554,7 @@
       </c>
     </row>
     <row r="147" spans="2:7">
-      <c r="B147" s="38"/>
+      <c r="B147" s="45"/>
       <c r="C147" s="31" t="s">
         <v>455</v>
       </c>
@@ -29569,7 +29569,7 @@
       </c>
     </row>
     <row r="148" spans="2:7">
-      <c r="B148" s="38"/>
+      <c r="B148" s="45"/>
       <c r="C148" s="31" t="s">
         <v>454</v>
       </c>
@@ -29584,7 +29584,7 @@
       </c>
     </row>
     <row r="149" spans="2:7">
-      <c r="B149" s="38"/>
+      <c r="B149" s="45"/>
       <c r="C149" s="31" t="s">
         <v>455</v>
       </c>
@@ -29599,7 +29599,7 @@
       </c>
     </row>
     <row r="150" spans="2:7">
-      <c r="B150" s="39" t="s">
+      <c r="B150" s="47" t="s">
         <v>456</v>
       </c>
       <c r="C150" s="31" t="s">
@@ -29619,7 +29619,7 @@
       </c>
     </row>
     <row r="151" spans="2:7">
-      <c r="B151" s="39"/>
+      <c r="B151" s="47"/>
       <c r="C151" s="31" t="s">
         <v>458</v>
       </c>
@@ -29637,7 +29637,7 @@
       </c>
     </row>
     <row r="152" spans="2:7">
-      <c r="B152" s="39"/>
+      <c r="B152" s="47"/>
       <c r="C152" s="31" t="s">
         <v>459</v>
       </c>
@@ -29652,7 +29652,7 @@
       </c>
     </row>
     <row r="153" spans="2:7">
-      <c r="B153" s="39"/>
+      <c r="B153" s="47"/>
       <c r="C153" s="31" t="s">
         <v>460</v>
       </c>
@@ -29670,7 +29670,7 @@
       </c>
     </row>
     <row r="154" spans="2:7">
-      <c r="B154" s="39" t="s">
+      <c r="B154" s="47" t="s">
         <v>461</v>
       </c>
       <c r="C154" s="31" t="s">
@@ -29684,7 +29684,7 @@
       </c>
     </row>
     <row r="155" spans="2:7">
-      <c r="B155" s="39"/>
+      <c r="B155" s="47"/>
       <c r="C155" s="31" t="s">
         <v>462</v>
       </c>
@@ -29696,7 +29696,7 @@
       </c>
     </row>
     <row r="156" spans="2:7">
-      <c r="B156" s="41" t="s">
+      <c r="B156" s="48" t="s">
         <v>463</v>
       </c>
       <c r="C156" s="33" t="s">
@@ -29710,7 +29710,7 @@
       </c>
     </row>
     <row r="157" spans="2:7">
-      <c r="B157" s="42"/>
+      <c r="B157" s="49"/>
       <c r="C157" s="33" t="s">
         <v>465</v>
       </c>
@@ -29722,7 +29722,7 @@
       </c>
     </row>
     <row r="158" spans="2:7">
-      <c r="B158" s="42"/>
+      <c r="B158" s="49"/>
       <c r="C158" s="33" t="s">
         <v>466</v>
       </c>
@@ -29734,7 +29734,7 @@
       </c>
     </row>
     <row r="159" spans="2:7">
-      <c r="B159" s="42"/>
+      <c r="B159" s="49"/>
       <c r="C159" s="33" t="s">
         <v>467</v>
       </c>
@@ -29746,7 +29746,7 @@
       </c>
     </row>
     <row r="160" spans="2:7">
-      <c r="B160" s="42"/>
+      <c r="B160" s="49"/>
       <c r="C160" s="33" t="s">
         <v>468</v>
       </c>
@@ -29758,7 +29758,7 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="42"/>
+      <c r="B161" s="49"/>
       <c r="C161" s="33" t="s">
         <v>469</v>
       </c>
@@ -29770,7 +29770,7 @@
       </c>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="42"/>
+      <c r="B162" s="49"/>
       <c r="C162" s="33" t="s">
         <v>470</v>
       </c>
@@ -29782,7 +29782,7 @@
       </c>
     </row>
     <row r="163" spans="2:6">
-      <c r="B163" s="42"/>
+      <c r="B163" s="49"/>
       <c r="C163" s="33" t="s">
         <v>471</v>
       </c>
@@ -29794,7 +29794,7 @@
       </c>
     </row>
     <row r="164" spans="2:6">
-      <c r="B164" s="41" t="s">
+      <c r="B164" s="48" t="s">
         <v>472</v>
       </c>
       <c r="C164" s="33" t="s">
@@ -29808,7 +29808,7 @@
       </c>
     </row>
     <row r="165" spans="2:6">
-      <c r="B165" s="42"/>
+      <c r="B165" s="49"/>
       <c r="C165" s="33" t="s">
         <v>474</v>
       </c>
@@ -29820,7 +29820,7 @@
       </c>
     </row>
     <row r="166" spans="2:6">
-      <c r="B166" s="39" t="s">
+      <c r="B166" s="47" t="s">
         <v>475</v>
       </c>
       <c r="C166" s="31" t="s">
@@ -29834,7 +29834,7 @@
       </c>
     </row>
     <row r="167" spans="2:6">
-      <c r="B167" s="38"/>
+      <c r="B167" s="45"/>
       <c r="C167" s="31" t="s">
         <v>477</v>
       </c>
@@ -29846,7 +29846,7 @@
       </c>
     </row>
     <row r="168" spans="2:6">
-      <c r="B168" s="38"/>
+      <c r="B168" s="45"/>
       <c r="C168" s="31" t="s">
         <v>478</v>
       </c>
@@ -29858,7 +29858,7 @@
       </c>
     </row>
     <row r="169" spans="2:6">
-      <c r="B169" s="38"/>
+      <c r="B169" s="45"/>
       <c r="C169" s="31" t="s">
         <v>479</v>
       </c>
@@ -29870,7 +29870,7 @@
       </c>
     </row>
     <row r="170" spans="2:6">
-      <c r="B170" s="38"/>
+      <c r="B170" s="45"/>
       <c r="C170" s="31" t="s">
         <v>480</v>
       </c>
@@ -29882,7 +29882,7 @@
       </c>
     </row>
     <row r="171" spans="2:6">
-      <c r="B171" s="38" t="s">
+      <c r="B171" s="45" t="s">
         <v>481</v>
       </c>
       <c r="C171" s="31" t="s">
@@ -29899,7 +29899,7 @@
       </c>
     </row>
     <row r="172" spans="2:6">
-      <c r="B172" s="38"/>
+      <c r="B172" s="45"/>
       <c r="C172" s="31" t="s">
         <v>483</v>
       </c>
@@ -29914,7 +29914,7 @@
       </c>
     </row>
     <row r="173" spans="2:6">
-      <c r="B173" s="38"/>
+      <c r="B173" s="45"/>
       <c r="C173" s="31" t="s">
         <v>484</v>
       </c>
@@ -29929,7 +29929,7 @@
       </c>
     </row>
     <row r="174" spans="2:6">
-      <c r="B174" s="38"/>
+      <c r="B174" s="45"/>
       <c r="C174" s="31" t="s">
         <v>485</v>
       </c>
@@ -29944,7 +29944,7 @@
       </c>
     </row>
     <row r="175" spans="2:6">
-      <c r="B175" s="38" t="s">
+      <c r="B175" s="45" t="s">
         <v>486</v>
       </c>
       <c r="C175" s="31" t="s">
@@ -29958,7 +29958,7 @@
       </c>
     </row>
     <row r="176" spans="2:6">
-      <c r="B176" s="38"/>
+      <c r="B176" s="45"/>
       <c r="C176" s="31" t="s">
         <v>487</v>
       </c>
@@ -29970,7 +29970,7 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="38"/>
+      <c r="B177" s="45"/>
       <c r="C177" s="31" t="s">
         <v>488</v>
       </c>
@@ -29982,7 +29982,7 @@
       </c>
     </row>
     <row r="178" spans="2:6">
-      <c r="B178" s="38"/>
+      <c r="B178" s="45"/>
       <c r="C178" s="31" t="s">
         <v>489</v>
       </c>
@@ -29994,7 +29994,7 @@
       </c>
     </row>
     <row r="179" spans="2:6">
-      <c r="B179" s="38"/>
+      <c r="B179" s="45"/>
       <c r="C179" s="31" t="s">
         <v>490</v>
       </c>
@@ -30006,7 +30006,7 @@
       </c>
     </row>
     <row r="180" spans="2:6">
-      <c r="B180" s="38"/>
+      <c r="B180" s="45"/>
       <c r="C180" s="31" t="s">
         <v>491</v>
       </c>
@@ -30021,7 +30021,7 @@
       </c>
     </row>
     <row r="181" spans="2:6">
-      <c r="B181" s="38"/>
+      <c r="B181" s="45"/>
       <c r="C181" s="31" t="s">
         <v>492</v>
       </c>
@@ -30036,7 +30036,7 @@
       </c>
     </row>
     <row r="182" spans="2:6">
-      <c r="B182" s="38" t="s">
+      <c r="B182" s="45" t="s">
         <v>493</v>
       </c>
       <c r="C182" s="31" t="s">
@@ -30050,7 +30050,7 @@
       </c>
     </row>
     <row r="183" spans="2:6">
-      <c r="B183" s="38"/>
+      <c r="B183" s="45"/>
       <c r="C183" s="31" t="s">
         <v>494</v>
       </c>
@@ -30062,7 +30062,7 @@
       </c>
     </row>
     <row r="184" spans="2:6">
-      <c r="B184" s="38"/>
+      <c r="B184" s="45"/>
       <c r="C184" s="31" t="s">
         <v>495</v>
       </c>
@@ -30074,7 +30074,7 @@
       </c>
     </row>
     <row r="185" spans="2:6">
-      <c r="B185" s="38" t="s">
+      <c r="B185" s="45" t="s">
         <v>496</v>
       </c>
       <c r="C185" s="31" t="s">
@@ -30088,7 +30088,7 @@
       </c>
     </row>
     <row r="186" spans="2:6">
-      <c r="B186" s="38"/>
+      <c r="B186" s="45"/>
       <c r="C186" s="31" t="s">
         <v>498</v>
       </c>
@@ -30100,7 +30100,7 @@
       </c>
     </row>
     <row r="187" spans="2:6">
-      <c r="B187" s="38"/>
+      <c r="B187" s="45"/>
       <c r="C187" s="31" t="s">
         <v>499</v>
       </c>
@@ -30112,7 +30112,7 @@
       </c>
     </row>
     <row r="188" spans="2:6">
-      <c r="B188" s="38"/>
+      <c r="B188" s="45"/>
       <c r="C188" s="31" t="s">
         <v>500</v>
       </c>
@@ -30124,7 +30124,7 @@
       </c>
     </row>
     <row r="189" spans="2:6">
-      <c r="B189" s="38"/>
+      <c r="B189" s="45"/>
       <c r="C189" s="31" t="s">
         <v>501</v>
       </c>
@@ -30136,7 +30136,7 @@
       </c>
     </row>
     <row r="190" spans="2:6">
-      <c r="B190" s="38"/>
+      <c r="B190" s="45"/>
       <c r="C190" s="31" t="s">
         <v>502</v>
       </c>
@@ -30148,7 +30148,7 @@
       </c>
     </row>
     <row r="191" spans="2:6">
-      <c r="B191" s="38"/>
+      <c r="B191" s="45"/>
       <c r="C191" s="31" t="s">
         <v>503</v>
       </c>
@@ -30160,7 +30160,7 @@
       </c>
     </row>
     <row r="192" spans="2:6">
-      <c r="B192" s="38"/>
+      <c r="B192" s="45"/>
       <c r="C192" s="31" t="s">
         <v>504</v>
       </c>
@@ -30172,7 +30172,7 @@
       </c>
     </row>
     <row r="193" spans="2:5">
-      <c r="B193" s="38"/>
+      <c r="B193" s="45"/>
       <c r="C193" s="31" t="s">
         <v>505</v>
       </c>
@@ -30184,7 +30184,7 @@
       </c>
     </row>
     <row r="194" spans="2:5">
-      <c r="B194" s="38"/>
+      <c r="B194" s="45"/>
       <c r="C194" s="31" t="s">
         <v>506</v>
       </c>
@@ -30196,7 +30196,7 @@
       </c>
     </row>
     <row r="195" spans="2:5">
-      <c r="B195" s="38"/>
+      <c r="B195" s="45"/>
       <c r="C195" s="31" t="s">
         <v>507</v>
       </c>
@@ -30208,7 +30208,7 @@
       </c>
     </row>
     <row r="196" spans="2:5">
-      <c r="B196" s="38"/>
+      <c r="B196" s="45"/>
       <c r="C196" s="31" t="s">
         <v>508</v>
       </c>
@@ -30220,7 +30220,7 @@
       </c>
     </row>
     <row r="197" spans="2:5">
-      <c r="B197" s="38"/>
+      <c r="B197" s="45"/>
       <c r="C197" s="31" t="s">
         <v>509</v>
       </c>
@@ -30232,7 +30232,7 @@
       </c>
     </row>
     <row r="198" spans="2:5">
-      <c r="B198" s="38"/>
+      <c r="B198" s="45"/>
       <c r="C198" s="31" t="s">
         <v>510</v>
       </c>
@@ -30244,7 +30244,7 @@
       </c>
     </row>
     <row r="199" spans="2:5">
-      <c r="B199" s="38"/>
+      <c r="B199" s="45"/>
       <c r="C199" s="31" t="s">
         <v>511</v>
       </c>
@@ -30256,7 +30256,7 @@
       </c>
     </row>
     <row r="200" spans="2:5">
-      <c r="B200" s="38" t="s">
+      <c r="B200" s="45" t="s">
         <v>512</v>
       </c>
       <c r="C200" s="31" t="s">
@@ -30270,7 +30270,7 @@
       </c>
     </row>
     <row r="201" spans="2:5">
-      <c r="B201" s="38"/>
+      <c r="B201" s="45"/>
       <c r="C201" s="31" t="s">
         <v>514</v>
       </c>
@@ -30282,7 +30282,7 @@
       </c>
     </row>
     <row r="202" spans="2:5">
-      <c r="B202" s="38"/>
+      <c r="B202" s="45"/>
       <c r="C202" s="31" t="s">
         <v>515</v>
       </c>
@@ -30294,7 +30294,7 @@
       </c>
     </row>
     <row r="203" spans="2:5">
-      <c r="B203" s="38"/>
+      <c r="B203" s="45"/>
       <c r="C203" s="31" t="s">
         <v>516</v>
       </c>
@@ -30306,7 +30306,7 @@
       </c>
     </row>
     <row r="204" spans="2:5">
-      <c r="B204" s="38"/>
+      <c r="B204" s="45"/>
       <c r="C204" s="31" t="s">
         <v>517</v>
       </c>
@@ -30318,7 +30318,7 @@
       </c>
     </row>
     <row r="205" spans="2:5">
-      <c r="B205" s="38"/>
+      <c r="B205" s="45"/>
       <c r="C205" s="31" t="s">
         <v>518</v>
       </c>
@@ -30330,7 +30330,7 @@
       </c>
     </row>
     <row r="206" spans="2:5">
-      <c r="B206" s="38"/>
+      <c r="B206" s="45"/>
       <c r="C206" s="31" t="s">
         <v>519</v>
       </c>
@@ -30342,7 +30342,7 @@
       </c>
     </row>
     <row r="207" spans="2:5">
-      <c r="B207" s="38"/>
+      <c r="B207" s="45"/>
       <c r="C207" s="31" t="s">
         <v>520</v>
       </c>
@@ -30354,7 +30354,7 @@
       </c>
     </row>
     <row r="208" spans="2:5">
-      <c r="B208" s="38"/>
+      <c r="B208" s="45"/>
       <c r="C208" s="31" t="s">
         <v>521</v>
       </c>
@@ -30366,7 +30366,7 @@
       </c>
     </row>
     <row r="209" spans="2:5">
-      <c r="B209" s="38"/>
+      <c r="B209" s="45"/>
       <c r="C209" s="31" t="s">
         <v>522</v>
       </c>
@@ -30378,7 +30378,7 @@
       </c>
     </row>
     <row r="210" spans="2:5">
-      <c r="B210" s="43" t="s">
+      <c r="B210" s="46" t="s">
         <v>523</v>
       </c>
       <c r="C210" s="33" t="s">
@@ -30392,7 +30392,7 @@
       </c>
     </row>
     <row r="211" spans="2:5">
-      <c r="B211" s="43"/>
+      <c r="B211" s="46"/>
       <c r="C211" s="33" t="s">
         <v>525</v>
       </c>
@@ -30404,7 +30404,7 @@
       </c>
     </row>
     <row r="212" spans="2:5">
-      <c r="B212" s="43"/>
+      <c r="B212" s="46"/>
       <c r="C212" s="33" t="s">
         <v>526</v>
       </c>
@@ -30416,7 +30416,7 @@
       </c>
     </row>
     <row r="213" spans="2:5">
-      <c r="B213" s="43"/>
+      <c r="B213" s="46"/>
       <c r="C213" s="33" t="s">
         <v>527</v>
       </c>
@@ -30428,7 +30428,7 @@
       </c>
     </row>
     <row r="214" spans="2:5">
-      <c r="B214" s="43"/>
+      <c r="B214" s="46"/>
       <c r="C214" s="33" t="s">
         <v>528</v>
       </c>
@@ -30440,7 +30440,7 @@
       </c>
     </row>
     <row r="215" spans="2:5">
-      <c r="B215" s="43"/>
+      <c r="B215" s="46"/>
       <c r="C215" s="33" t="s">
         <v>529</v>
       </c>
@@ -30452,7 +30452,7 @@
       </c>
     </row>
     <row r="216" spans="2:5">
-      <c r="B216" s="43"/>
+      <c r="B216" s="46"/>
       <c r="C216" s="33" t="s">
         <v>530</v>
       </c>
@@ -30464,7 +30464,7 @@
       </c>
     </row>
     <row r="217" spans="2:5">
-      <c r="B217" s="43"/>
+      <c r="B217" s="46"/>
       <c r="C217" s="33" t="s">
         <v>531</v>
       </c>
@@ -30476,7 +30476,7 @@
       </c>
     </row>
     <row r="218" spans="2:5">
-      <c r="B218" s="43"/>
+      <c r="B218" s="46"/>
       <c r="C218" s="33" t="s">
         <v>532</v>
       </c>
@@ -30488,7 +30488,7 @@
       </c>
     </row>
     <row r="219" spans="2:5">
-      <c r="B219" s="43"/>
+      <c r="B219" s="46"/>
       <c r="C219" s="33" t="s">
         <v>533</v>
       </c>
@@ -30500,7 +30500,7 @@
       </c>
     </row>
     <row r="220" spans="2:5">
-      <c r="B220" s="43"/>
+      <c r="B220" s="46"/>
       <c r="C220" s="33" t="s">
         <v>534</v>
       </c>
@@ -30512,7 +30512,7 @@
       </c>
     </row>
     <row r="221" spans="2:5">
-      <c r="B221" s="43"/>
+      <c r="B221" s="46"/>
       <c r="C221" s="33" t="s">
         <v>535</v>
       </c>
@@ -30524,7 +30524,7 @@
       </c>
     </row>
     <row r="222" spans="2:5">
-      <c r="B222" s="43"/>
+      <c r="B222" s="46"/>
       <c r="C222" s="33" t="s">
         <v>536</v>
       </c>
@@ -30536,7 +30536,7 @@
       </c>
     </row>
     <row r="223" spans="2:5">
-      <c r="B223" s="43"/>
+      <c r="B223" s="46"/>
       <c r="C223" s="33" t="s">
         <v>537</v>
       </c>
@@ -30548,7 +30548,7 @@
       </c>
     </row>
     <row r="224" spans="2:5">
-      <c r="B224" s="43"/>
+      <c r="B224" s="46"/>
       <c r="C224" s="33" t="s">
         <v>538</v>
       </c>
@@ -30560,7 +30560,7 @@
       </c>
     </row>
     <row r="225" spans="2:5">
-      <c r="B225" s="43"/>
+      <c r="B225" s="46"/>
       <c r="C225" s="33" t="s">
         <v>539</v>
       </c>
@@ -30572,7 +30572,7 @@
       </c>
     </row>
     <row r="226" spans="2:5">
-      <c r="B226" s="43"/>
+      <c r="B226" s="46"/>
       <c r="C226" s="33" t="s">
         <v>540</v>
       </c>
@@ -30584,7 +30584,7 @@
       </c>
     </row>
     <row r="227" spans="2:5">
-      <c r="B227" s="43"/>
+      <c r="B227" s="46"/>
       <c r="C227" s="33" t="s">
         <v>541</v>
       </c>
@@ -30596,7 +30596,7 @@
       </c>
     </row>
     <row r="228" spans="2:5">
-      <c r="B228" s="43"/>
+      <c r="B228" s="46"/>
       <c r="C228" s="33" t="s">
         <v>542</v>
       </c>
@@ -30608,7 +30608,7 @@
       </c>
     </row>
     <row r="229" spans="2:5">
-      <c r="B229" s="43"/>
+      <c r="B229" s="46"/>
       <c r="C229" s="33" t="s">
         <v>543</v>
       </c>
@@ -30620,7 +30620,7 @@
       </c>
     </row>
     <row r="230" spans="2:5">
-      <c r="B230" s="43"/>
+      <c r="B230" s="46"/>
       <c r="C230" s="33" t="s">
         <v>544</v>
       </c>
@@ -30632,7 +30632,7 @@
       </c>
     </row>
     <row r="231" spans="2:5">
-      <c r="B231" s="43"/>
+      <c r="B231" s="46"/>
       <c r="C231" s="33" t="s">
         <v>545</v>
       </c>
@@ -30644,7 +30644,7 @@
       </c>
     </row>
     <row r="232" spans="2:5">
-      <c r="B232" s="43"/>
+      <c r="B232" s="46"/>
       <c r="C232" s="33" t="s">
         <v>546</v>
       </c>
@@ -30656,7 +30656,7 @@
       </c>
     </row>
     <row r="233" spans="2:5">
-      <c r="B233" s="43"/>
+      <c r="B233" s="46"/>
       <c r="C233" s="33" t="s">
         <v>547</v>
       </c>
@@ -30668,7 +30668,7 @@
       </c>
     </row>
     <row r="234" spans="2:5">
-      <c r="B234" s="43"/>
+      <c r="B234" s="46"/>
       <c r="C234" s="33" t="s">
         <v>548</v>
       </c>
@@ -30680,7 +30680,7 @@
       </c>
     </row>
     <row r="235" spans="2:5">
-      <c r="B235" s="43"/>
+      <c r="B235" s="46"/>
       <c r="C235" s="33" t="s">
         <v>549</v>
       </c>
@@ -30692,7 +30692,7 @@
       </c>
     </row>
     <row r="236" spans="2:5">
-      <c r="B236" s="43"/>
+      <c r="B236" s="46"/>
       <c r="C236" s="33" t="s">
         <v>550</v>
       </c>
@@ -30704,7 +30704,7 @@
       </c>
     </row>
     <row r="237" spans="2:5">
-      <c r="B237" s="43"/>
+      <c r="B237" s="46"/>
       <c r="C237" s="33" t="s">
         <v>551</v>
       </c>
@@ -30716,7 +30716,7 @@
       </c>
     </row>
     <row r="238" spans="2:5">
-      <c r="B238" s="43"/>
+      <c r="B238" s="46"/>
       <c r="C238" s="33" t="s">
         <v>552</v>
       </c>
@@ -30728,7 +30728,7 @@
       </c>
     </row>
     <row r="239" spans="2:5">
-      <c r="B239" s="43"/>
+      <c r="B239" s="46"/>
       <c r="C239" s="33" t="s">
         <v>553</v>
       </c>
@@ -30740,7 +30740,7 @@
       </c>
     </row>
     <row r="240" spans="2:5">
-      <c r="B240" s="43"/>
+      <c r="B240" s="46"/>
       <c r="C240" s="33" t="s">
         <v>554</v>
       </c>
@@ -30752,7 +30752,7 @@
       </c>
     </row>
     <row r="241" spans="2:7">
-      <c r="B241" s="43"/>
+      <c r="B241" s="46"/>
       <c r="C241" s="33" t="s">
         <v>555</v>
       </c>
@@ -30764,7 +30764,7 @@
       </c>
     </row>
     <row r="242" spans="2:7">
-      <c r="B242" s="43"/>
+      <c r="B242" s="46"/>
       <c r="C242" s="33" t="s">
         <v>556</v>
       </c>
@@ -30776,7 +30776,7 @@
       </c>
     </row>
     <row r="243" spans="2:7">
-      <c r="B243" s="43"/>
+      <c r="B243" s="46"/>
       <c r="C243" s="33" t="s">
         <v>557</v>
       </c>
@@ -30788,7 +30788,7 @@
       </c>
     </row>
     <row r="244" spans="2:7">
-      <c r="B244" s="38" t="s">
+      <c r="B244" s="45" t="s">
         <v>558</v>
       </c>
       <c r="C244" s="31" t="s">
@@ -30799,7 +30799,7 @@
       </c>
     </row>
     <row r="245" spans="2:7">
-      <c r="B245" s="38"/>
+      <c r="B245" s="45"/>
       <c r="C245" s="31" t="s">
         <v>560</v>
       </c>
@@ -30808,7 +30808,7 @@
       </c>
     </row>
     <row r="246" spans="2:7">
-      <c r="B246" s="38"/>
+      <c r="B246" s="45"/>
       <c r="C246" s="31" t="s">
         <v>561</v>
       </c>
@@ -30817,7 +30817,7 @@
       </c>
     </row>
     <row r="247" spans="2:7">
-      <c r="B247" s="38" t="s">
+      <c r="B247" s="45" t="s">
         <v>562</v>
       </c>
       <c r="C247" s="31" t="s">
@@ -30837,7 +30837,7 @@
       </c>
     </row>
     <row r="248" spans="2:7">
-      <c r="B248" s="38"/>
+      <c r="B248" s="45"/>
       <c r="C248" s="31" t="s">
         <v>564</v>
       </c>
@@ -30853,7 +30853,7 @@
       </c>
     </row>
     <row r="249" spans="2:7">
-      <c r="B249" s="38"/>
+      <c r="B249" s="45"/>
       <c r="C249" s="31" t="s">
         <v>1298</v>
       </c>
@@ -30869,7 +30869,7 @@
       </c>
     </row>
     <row r="250" spans="2:7">
-      <c r="B250" s="38"/>
+      <c r="B250" s="45"/>
       <c r="C250" s="31" t="s">
         <v>1301</v>
       </c>
@@ -30885,7 +30885,7 @@
       </c>
     </row>
     <row r="251" spans="2:7">
-      <c r="B251" s="38"/>
+      <c r="B251" s="45"/>
       <c r="C251" s="31" t="s">
         <v>1303</v>
       </c>
@@ -30901,7 +30901,7 @@
       </c>
     </row>
     <row r="252" spans="2:7">
-      <c r="B252" s="38"/>
+      <c r="B252" s="45"/>
       <c r="C252" s="31" t="s">
         <v>1305</v>
       </c>
@@ -30917,7 +30917,7 @@
       </c>
     </row>
     <row r="253" spans="2:7">
-      <c r="B253" s="38"/>
+      <c r="B253" s="45"/>
       <c r="C253" s="31" t="s">
         <v>1307</v>
       </c>
@@ -30933,7 +30933,7 @@
       </c>
     </row>
     <row r="254" spans="2:7">
-      <c r="B254" s="38"/>
+      <c r="B254" s="45"/>
       <c r="C254" s="31" t="s">
         <v>1309</v>
       </c>
@@ -30949,7 +30949,7 @@
       </c>
     </row>
     <row r="255" spans="2:7">
-      <c r="B255" s="38"/>
+      <c r="B255" s="45"/>
       <c r="C255" s="31" t="s">
         <v>1311</v>
       </c>
@@ -30965,7 +30965,7 @@
       </c>
     </row>
     <row r="256" spans="2:7">
-      <c r="B256" s="38"/>
+      <c r="B256" s="45"/>
       <c r="C256" s="31" t="s">
         <v>1313</v>
       </c>
@@ -30981,7 +30981,7 @@
       </c>
     </row>
     <row r="257" spans="2:7">
-      <c r="B257" s="38"/>
+      <c r="B257" s="45"/>
       <c r="C257" s="31" t="s">
         <v>565</v>
       </c>
@@ -30997,7 +30997,7 @@
       </c>
     </row>
     <row r="258" spans="2:7">
-      <c r="B258" s="38"/>
+      <c r="B258" s="45"/>
       <c r="C258" s="31" t="s">
         <v>1318</v>
       </c>
@@ -31013,7 +31013,7 @@
       </c>
     </row>
     <row r="259" spans="2:7">
-      <c r="B259" s="38"/>
+      <c r="B259" s="45"/>
       <c r="C259" s="31" t="s">
         <v>566</v>
       </c>
@@ -31029,7 +31029,7 @@
       </c>
     </row>
     <row r="260" spans="2:7">
-      <c r="B260" s="38"/>
+      <c r="B260" s="45"/>
       <c r="C260" s="31" t="s">
         <v>567</v>
       </c>
@@ -31045,7 +31045,7 @@
       </c>
     </row>
     <row r="261" spans="2:7">
-      <c r="B261" s="38"/>
+      <c r="B261" s="45"/>
       <c r="C261" s="31" t="s">
         <v>1322</v>
       </c>
@@ -31061,7 +31061,7 @@
       </c>
     </row>
     <row r="262" spans="2:7">
-      <c r="B262" s="38"/>
+      <c r="B262" s="45"/>
       <c r="C262" s="31" t="s">
         <v>568</v>
       </c>
@@ -31077,7 +31077,7 @@
       </c>
     </row>
     <row r="263" spans="2:7">
-      <c r="B263" s="38"/>
+      <c r="B263" s="45"/>
       <c r="C263" s="31" t="s">
         <v>1325</v>
       </c>
@@ -31093,7 +31093,7 @@
       </c>
     </row>
     <row r="264" spans="2:7">
-      <c r="B264" s="38"/>
+      <c r="B264" s="45"/>
       <c r="C264" s="31" t="s">
         <v>1327</v>
       </c>
@@ -31109,7 +31109,7 @@
       </c>
     </row>
     <row r="265" spans="2:7">
-      <c r="B265" s="38"/>
+      <c r="B265" s="45"/>
       <c r="C265" s="31" t="s">
         <v>1329</v>
       </c>
@@ -31125,7 +31125,7 @@
       </c>
     </row>
     <row r="266" spans="2:7">
-      <c r="B266" s="38"/>
+      <c r="B266" s="45"/>
       <c r="C266" s="31" t="s">
         <v>1331</v>
       </c>
@@ -31141,7 +31141,7 @@
       </c>
     </row>
     <row r="267" spans="2:7">
-      <c r="B267" s="38"/>
+      <c r="B267" s="45"/>
       <c r="C267" s="31" t="s">
         <v>569</v>
       </c>
@@ -31150,7 +31150,7 @@
       </c>
     </row>
     <row r="268" spans="2:7">
-      <c r="B268" s="38"/>
+      <c r="B268" s="45"/>
       <c r="C268" s="31" t="s">
         <v>570</v>
       </c>
@@ -31159,7 +31159,7 @@
       </c>
     </row>
     <row r="269" spans="2:7">
-      <c r="B269" s="38"/>
+      <c r="B269" s="45"/>
       <c r="C269" s="31" t="s">
         <v>571</v>
       </c>
@@ -31168,7 +31168,7 @@
       </c>
     </row>
     <row r="270" spans="2:7">
-      <c r="B270" s="38"/>
+      <c r="B270" s="45"/>
       <c r="C270" s="31" t="s">
         <v>572</v>
       </c>
@@ -31177,7 +31177,7 @@
       </c>
     </row>
     <row r="271" spans="2:7">
-      <c r="B271" s="38"/>
+      <c r="B271" s="45"/>
       <c r="C271" s="31" t="s">
         <v>573</v>
       </c>
@@ -31186,7 +31186,7 @@
       </c>
     </row>
     <row r="272" spans="2:7">
-      <c r="B272" s="38"/>
+      <c r="B272" s="45"/>
       <c r="C272" s="31" t="s">
         <v>574</v>
       </c>
@@ -31195,7 +31195,7 @@
       </c>
     </row>
     <row r="273" spans="2:5">
-      <c r="B273" s="38" t="s">
+      <c r="B273" s="45" t="s">
         <v>575</v>
       </c>
       <c r="C273" s="31" t="s">
@@ -31209,7 +31209,7 @@
       </c>
     </row>
     <row r="274" spans="2:5">
-      <c r="B274" s="38"/>
+      <c r="B274" s="45"/>
       <c r="C274" s="31" t="s">
         <v>577</v>
       </c>
@@ -31221,7 +31221,7 @@
       </c>
     </row>
     <row r="275" spans="2:5">
-      <c r="B275" s="38"/>
+      <c r="B275" s="45"/>
       <c r="C275" s="31" t="s">
         <v>578</v>
       </c>
@@ -31233,7 +31233,7 @@
       </c>
     </row>
     <row r="276" spans="2:5">
-      <c r="B276" s="38"/>
+      <c r="B276" s="45"/>
       <c r="C276" s="31" t="s">
         <v>579</v>
       </c>
@@ -31245,7 +31245,7 @@
       </c>
     </row>
     <row r="277" spans="2:5">
-      <c r="B277" s="38"/>
+      <c r="B277" s="45"/>
       <c r="C277" s="31" t="s">
         <v>580</v>
       </c>
@@ -31257,7 +31257,7 @@
       </c>
     </row>
     <row r="278" spans="2:5">
-      <c r="B278" s="38"/>
+      <c r="B278" s="45"/>
       <c r="C278" s="31" t="s">
         <v>581</v>
       </c>
@@ -31269,7 +31269,7 @@
       </c>
     </row>
     <row r="279" spans="2:5">
-      <c r="B279" s="38"/>
+      <c r="B279" s="45"/>
       <c r="C279" s="31" t="s">
         <v>582</v>
       </c>
@@ -31281,7 +31281,7 @@
       </c>
     </row>
     <row r="280" spans="2:5">
-      <c r="B280" s="38"/>
+      <c r="B280" s="45"/>
       <c r="C280" s="31" t="s">
         <v>583</v>
       </c>
@@ -31293,7 +31293,7 @@
       </c>
     </row>
     <row r="281" spans="2:5">
-      <c r="B281" s="38"/>
+      <c r="B281" s="45"/>
       <c r="C281" s="31" t="s">
         <v>584</v>
       </c>
@@ -31305,7 +31305,7 @@
       </c>
     </row>
     <row r="282" spans="2:5">
-      <c r="B282" s="38"/>
+      <c r="B282" s="45"/>
       <c r="C282" s="31" t="s">
         <v>585</v>
       </c>
@@ -31317,7 +31317,7 @@
       </c>
     </row>
     <row r="283" spans="2:5">
-      <c r="B283" s="38"/>
+      <c r="B283" s="45"/>
       <c r="C283" s="31" t="s">
         <v>586</v>
       </c>
@@ -31329,7 +31329,7 @@
       </c>
     </row>
     <row r="284" spans="2:5">
-      <c r="B284" s="38"/>
+      <c r="B284" s="45"/>
       <c r="C284" s="31" t="s">
         <v>587</v>
       </c>
@@ -31342,14 +31342,24 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B182:B184"/>
-    <mergeCell ref="B273:B284"/>
-    <mergeCell ref="B175:B181"/>
-    <mergeCell ref="B185:B199"/>
-    <mergeCell ref="B200:B209"/>
-    <mergeCell ref="B210:B243"/>
-    <mergeCell ref="B244:B246"/>
-    <mergeCell ref="B247:B272"/>
+    <mergeCell ref="B38:B46"/>
+    <mergeCell ref="B2:B20"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B126:B130"/>
+    <mergeCell ref="B47:B53"/>
+    <mergeCell ref="B54:B61"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="B67:B78"/>
+    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="B99:B120"/>
+    <mergeCell ref="B121:B125"/>
     <mergeCell ref="B171:B174"/>
     <mergeCell ref="B131:B132"/>
     <mergeCell ref="B133:B138"/>
@@ -31362,24 +31372,14 @@
     <mergeCell ref="B150:B153"/>
     <mergeCell ref="B164:B165"/>
     <mergeCell ref="B166:B170"/>
-    <mergeCell ref="B126:B130"/>
-    <mergeCell ref="B47:B53"/>
-    <mergeCell ref="B54:B61"/>
-    <mergeCell ref="B62:B66"/>
-    <mergeCell ref="B67:B78"/>
-    <mergeCell ref="B79:B84"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B96:B98"/>
-    <mergeCell ref="B99:B120"/>
-    <mergeCell ref="B121:B125"/>
-    <mergeCell ref="B38:B46"/>
-    <mergeCell ref="B2:B20"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B182:B184"/>
+    <mergeCell ref="B273:B284"/>
+    <mergeCell ref="B175:B181"/>
+    <mergeCell ref="B185:B199"/>
+    <mergeCell ref="B200:B209"/>
+    <mergeCell ref="B210:B243"/>
+    <mergeCell ref="B244:B246"/>
+    <mergeCell ref="B247:B272"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
